--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>仮置きにより計画素案へ反映した38件と、令和8年10月30日までに決着をいただきたい事項。</t>
+          <t>仮置きにより計画素案へ反映した46件と、令和8年10月30日までに決着をいただきたい事項。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2646,331 +2646,251 @@
       <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr"/>
     </row>
-    <row r="44"/>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="4" t="inlineStr"/>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>決着しない場合の受託者の扱い</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>宛先</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>No.33</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>第6章第6節</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>所得段階は第9期の条例による16段階と公費による軽減前の割合を据え置いて算定し、政令の公布後に再算定する旨を明示した</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>No.39</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>第4章第3節</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIは第9期計画の目標指標を引き継ぎ、別の指標を新たに起こしていないこと及び改称により第9期の系列と接続しないことを明示した</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>No.40</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>第2章第3節5</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数は延べの値となるため、供給の担い手の分析には施設単位の実人数を用いる旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B47" s="21" t="n">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>No.43</t>
+        </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>第2章第1節3・第5章 基本目標5</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F47" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>申請から二次判定までの平均所要日数が法定の30日を上回っていることを掲げ、期間の短縮を要介護認定の適正化の取組に加えた</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" s="21" t="n">
-        <v>50</v>
+        <v>43</v>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>No.45</t>
+        </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>第4章第3節・第5章 基本目標5・資料1</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPI H15の分母を計画の標準給付費見込額とし、実績側は介護保険特別会計決算の保険給付費によることとした</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr"/>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B49" s="21" t="n">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>No.57</t>
+        </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F49" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>第9期に計画値を0としていた認知症対応型通所介護は算定値を置き、介護療養型医療施設は計上しないこととした</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B50" s="21" t="n">
-        <v>53</v>
+        <v>45</v>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>No.58</t>
+        </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>第6章第2節・第4節1</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>定期巡回・随時対応型訪問介護看護及び看護小規模多機能型居宅介護は自然体の算定値を置き、整備又は事業の実施による上乗せは含めないこととした</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B51" s="21" t="n">
-        <v>63</v>
+        <v>46</v>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>No.63</t>
+        </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F51" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="40" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B52" s="21" t="n">
-        <v>65</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>広域連合において行うべき事業の優先順位</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F52" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="40" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B53" s="21" t="n">
-        <v>67</v>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F53" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="40" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B54" s="21" t="n">
-        <v>68</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F54" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+          <t>人口の基礎は案C（地方創生総合戦略と住民基本台帳の実績趨勢）のままとし、3町の人口目標を一律に用いられない理由を注に明示した</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>決着しない場合の受託者の扱い</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>宛先</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B55" s="21" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F55" s="21" t="inlineStr">
@@ -2986,19 +2906,19 @@
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B56" s="21" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3008,7 +2928,7 @@
       </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -3019,24 +2939,24 @@
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B57" s="21" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F57" s="21" t="inlineStr">
@@ -3052,19 +2972,19 @@
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B58" s="21" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -3085,24 +3005,24 @@
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B59" s="21" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F59" s="21" t="inlineStr">
@@ -3118,19 +3038,19 @@
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B60" s="21" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -3151,19 +3071,19 @@
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B61" s="21" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -3184,19 +3104,19 @@
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B62" s="21" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -3217,24 +3137,24 @@
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B63" s="21" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
@@ -3244,25 +3164,25 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B64" s="21" t="n">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -3272,7 +3192,7 @@
       </c>
       <c r="F64" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3283,24 +3203,24 @@
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B65" s="21" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
@@ -3316,19 +3236,19 @@
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B66" s="21" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -3349,19 +3269,19 @@
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B67" s="21" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -3382,24 +3302,24 @@
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B68" s="21" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F68" s="21" t="inlineStr">
@@ -3415,19 +3335,19 @@
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" s="5" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B69" s="21" t="n">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -3448,19 +3368,19 @@
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" s="5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B70" s="21" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -3481,19 +3401,19 @@
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B71" s="21" t="n">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -3508,25 +3428,25 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部回答済</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" s="5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B72" s="21" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3547,19 +3467,19 @@
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" s="5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B73" s="21" t="n">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3580,19 +3500,19 @@
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B74" s="21" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -3613,24 +3533,24 @@
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" s="5" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B75" s="21" t="n">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
@@ -3646,24 +3566,24 @@
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" s="5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B76" s="21" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>混合型特定施設の必要利用定員総数を定めるか</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F76" s="21" t="inlineStr">
@@ -3679,19 +3599,19 @@
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" s="5" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B77" s="21" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3712,19 +3632,19 @@
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B78" s="21" t="n">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -3745,19 +3665,19 @@
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B79" s="21" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -3778,19 +3698,19 @@
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B80" s="21" t="n">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -3811,19 +3731,19 @@
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" s="5" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B81" s="21" t="n">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -3844,29 +3764,29 @@
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" s="5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B82" s="21" t="n">
-        <v>2</v>
+        <v>137</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F82" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -3877,29 +3797,29 @@
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" s="5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B83" s="21" t="n">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -3910,19 +3830,19 @@
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" s="5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B84" s="21" t="n">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -3932,7 +3852,7 @@
       </c>
       <c r="F84" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -3943,29 +3863,29 @@
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" s="5" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B85" s="21" t="n">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
@@ -3976,29 +3896,29 @@
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" s="5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B86" s="21" t="n">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F86" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -4009,19 +3929,19 @@
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" s="5" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B87" s="21" t="n">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -4031,7 +3951,7 @@
       </c>
       <c r="F87" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
@@ -4042,19 +3962,19 @@
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B88" s="21" t="n">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -4064,7 +3984,7 @@
       </c>
       <c r="F88" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
@@ -4075,19 +3995,19 @@
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B89" s="21" t="n">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -4097,7 +4017,7 @@
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
@@ -4108,24 +4028,24 @@
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B90" s="21" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
@@ -4141,24 +4061,24 @@
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B91" s="21" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
@@ -4174,19 +4094,19 @@
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B92" s="21" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -4207,24 +4127,24 @@
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B93" s="21" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
@@ -4240,24 +4160,24 @@
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B94" s="21" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
@@ -4273,24 +4193,24 @@
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B95" s="21" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
@@ -4306,19 +4226,19 @@
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" s="5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B96" s="21" t="n">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -4339,19 +4259,19 @@
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B97" s="21" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -4372,24 +4292,24 @@
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B98" s="21" t="n">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F98" s="21" t="inlineStr">
@@ -4405,24 +4325,24 @@
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B99" s="21" t="n">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
@@ -4438,19 +4358,19 @@
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" s="5" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B100" s="21" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -4471,19 +4391,19 @@
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" s="5" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B101" s="21" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -4504,24 +4424,24 @@
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" s="5" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B102" s="21" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F102" s="21" t="inlineStr">
@@ -4537,24 +4457,24 @@
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" s="5" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B103" s="21" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
@@ -4570,19 +4490,19 @@
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" s="5" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B104" s="21" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -4603,24 +4523,24 @@
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" s="5" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B105" s="21" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F105" s="21" t="inlineStr">
@@ -4636,24 +4556,24 @@
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" s="5" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B106" s="21" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr">
@@ -4669,19 +4589,19 @@
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" s="5" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B107" s="21" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -4702,24 +4622,24 @@
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" s="5" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B108" s="21" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr">
@@ -4735,24 +4655,24 @@
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" s="5" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B109" s="21" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
@@ -4768,19 +4688,19 @@
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" s="5" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B110" s="21" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -4801,19 +4721,19 @@
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" s="5" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B111" s="21" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -4834,19 +4754,19 @@
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" s="5" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B112" s="21" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -4867,24 +4787,24 @@
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" s="5" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B113" s="21" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F113" s="21" t="inlineStr">
@@ -4900,19 +4820,19 @@
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" s="5" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B114" s="21" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -4933,24 +4853,24 @@
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" s="5" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B115" s="21" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F115" s="21" t="inlineStr">
@@ -4966,24 +4886,24 @@
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" s="5" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B116" s="21" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F116" s="21" t="inlineStr">
@@ -4999,24 +4919,24 @@
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" s="5" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B117" s="21" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F117" s="21" t="inlineStr">
@@ -5026,30 +4946,30 @@
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" s="5" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B118" s="21" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F118" s="21" t="inlineStr">
@@ -5065,19 +4985,19 @@
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" s="5" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B119" s="21" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -5098,19 +5018,19 @@
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" s="5" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B120" s="21" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -5125,30 +5045,30 @@
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" s="5" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B121" s="21" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F121" s="21" t="inlineStr">
@@ -5164,42 +5084,306 @@
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B122" s="21" t="n">
+        <v>129</v>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの利用率等の伸びの選択</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F122" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B123" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B124" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B125" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>一部確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B126" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F126" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B127" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B128" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F128" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B129" s="21" t="n">
+        <v>164</v>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B122" s="21" t="n">
+      <c r="B130" s="21" t="n">
         <v>170</v>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F122" s="21" t="inlineStr">
+      <c r="F130" s="21" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="G130" s="6" t="inlineStr">
         <is>
           <t>一部解消</t>
         </is>
       </c>
     </row>
-    <row r="123"/>
-    <row r="124" ht="48" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>注1）仮置きにより計画素案へ反映した事項は38件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
+    <row r="131"/>
+    <row r="132" ht="48" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>注1）仮置きにより計画素案へ反映した事項は46件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。いずれにも決着しない場合の扱いを置いています。
 注3）未決160件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
@@ -5208,10 +5392,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A132:G132"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5977,7 +6161,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>38件／台帳にないもの なし</t>
+          <t>46件／台帳にないもの なし</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決160件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決161件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -5379,23 +5379,56 @@
         </is>
       </c>
     </row>
-    <row r="131"/>
-    <row r="132" ht="48" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B131" s="21" t="n">
+        <v>174</v>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="132"/>
+    <row r="133" ht="48" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>注1）仮置きにより計画素案へ反映した事項は46件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
-注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決160件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
+注3）未決161件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A132:G132"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A133:G133"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6186,7 +6219,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>76件／既定値のないもの なし</t>
+          <t>77件／既定値のないもの なし</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決161件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決164件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
         <is>
           <t>注1）仮置きにより計画素案へ反映した事項は46件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決161件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+注3）未決164件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>仮置きにより計画素案へ反映した46件と、令和8年10月30日までに決着をいただきたい事項。</t>
+          <t>仮置きにより計画素案へ反映した62件と、令和8年10月30日までに決着をいただきたい事項。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2830,595 +2830,435 @@
       <c r="F51" s="6" t="inlineStr"/>
       <c r="G51" s="6" t="inlineStr"/>
     </row>
-    <row r="52"/>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="4" t="inlineStr"/>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>決着しない場合の受託者の扱い</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>宛先</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>No.65</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとし、計画には優先順位そのものを掲げていない</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>No.66</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>第2章第3節</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）によることとし、出所により事業所数が異なることは時点と把握の範囲の違いによる旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>No.67</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>第6章第3節・第6節</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>当方の算定のまま進め、国の様式との対応は別に対照表として掲げることとし、その所在を第6章第6節の注に示した</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="21" t="n">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>No.68</t>
+        </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>見える化システムの自然体推計の再出力を受けられないものとして、当方の要介護度別の算定を採り、見える化システムの値は社人研の推計人口を基礎とするものである旨を給付費の置き方の対比に明示した</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="21" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>No.70</t>
+        </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>保険者機能強化推進交付金等の全国順位は計画本文に掲げず、策定委員会の資料にとどめた（第3章第4節は対全国比までを掲げる）</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="21" t="n">
         <v>52</v>
       </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>No.73</t>
+        </is>
+      </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>第5章 基本目標5</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F57" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>ケアプラン点検実施要領は協議資料にとどめ、計画本文には令和9年度当初に実施要領を定めることと点検件数・改善率・再指摘率の目標のみを掲げた</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B58" s="21" t="n">
         <v>53</v>
       </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>No.75</t>
+        </is>
+      </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F58" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPIと改善事項は当方の再整理案のままとし、計画本文の成果指標は現行の12項目のまま置いた（再整理案のご了承を受けた時点で置き換える）</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B59" s="21" t="n">
-        <v>63</v>
+        <v>54</v>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>No.76</t>
+        </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPI H03は、年齢階級別及び過年度分の抽出が確認できないため未算定のままとし、データ源と未算定である理由を注に明示した</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B60" s="21" t="n">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>No.77</t>
+        </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F60" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPI H14は、北海道の評価指標⑥の団体別の値を引用できないものとして補完指標にとどめ、目標値を置かないこととした</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B61" s="21" t="n">
-        <v>67</v>
+        <v>56</v>
+      </c>
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>No.78</t>
+        </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>第2章第3節</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F61" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認知症対応型共同生活介護の定員は北海道の名簿によるものとし、既存の事業所における定員の変更の有無は［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="21" t="n">
-        <v>68</v>
+        <v>57</v>
+      </c>
+      <c r="B62" s="21" t="inlineStr">
+        <is>
+          <t>No.79</t>
+        </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F62" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>第9期の19施策の体系を維持し、施策数の見直しは行わなかった</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B63" s="21" t="n">
-        <v>78</v>
+        <v>58</v>
+      </c>
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t>No.81</t>
+        </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>第4章第3節・第5章 基本目標5・資料1</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>発注者・美瑛町</t>
-        </is>
-      </c>
-      <c r="F63" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPI H16は、給付実績の明細（加算・減算の単位）が得られないため、指定・指定の更新・運営指導の際に業務継続計画の策定を確認した地域密着型サービス事業所（17事業所）の割合に改めた</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B64" s="21" t="n">
-        <v>82</v>
+        <v>59</v>
+      </c>
+      <c r="B64" s="21" t="inlineStr">
+        <is>
+          <t>No.95</t>
+        </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>第6章第4節</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F64" s="21" t="inlineStr">
-        <is>
-          <t>R8.9.24</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>基準条例の内容は計画に掲げず、協力医療機関に関する規定を令和9年4月1日までに条例において整える必要があることを［要確認］として明示した</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B65" s="21" t="n">
-        <v>88</v>
+        <v>60</v>
+      </c>
+      <c r="B65" s="21" t="inlineStr">
+        <is>
+          <t>No.96</t>
+        </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>第2章第3節6・第6章第4節4</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F65" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げ、必要利用定員総数は3町への照会により定員を確定したうえで定めることを注に明示した</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B66" s="21" t="n">
-        <v>95</v>
+        <v>61</v>
+      </c>
+      <c r="B66" s="21" t="inlineStr">
+        <is>
+          <t>No.102</t>
+        </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F66" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>令和8年度（4か月）を基準年度に用いない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr"/>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B67" s="21" t="n">
-        <v>96</v>
+        <v>62</v>
+      </c>
+      <c r="B67" s="21" t="inlineStr">
+        <is>
+          <t>No.122</t>
+        </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F67" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="40" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B68" s="21" t="n">
-        <v>98</v>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F68" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="40" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B69" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F69" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="40" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B70" s="21" t="n">
-        <v>101</v>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F70" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+          <t>転載を禁ずる旨の記載がある受領資料2件は成果品に用いず、原典のみを引いた（計画素案に当該2件からの記述はない）</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68"/>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="4" t="inlineStr"/>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>決着しない場合の受託者の扱い</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>宛先</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" s="5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B71" s="21" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F71" s="21" t="inlineStr">
@@ -3428,25 +3268,25 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" s="5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B72" s="21" t="n">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -3467,19 +3307,19 @@
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" s="5" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B73" s="21" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -3500,19 +3340,19 @@
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B74" s="21" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -3533,24 +3373,24 @@
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" s="5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B75" s="21" t="n">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
@@ -3566,24 +3406,24 @@
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" s="5" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B76" s="21" t="n">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F76" s="21" t="inlineStr">
@@ -3599,19 +3439,19 @@
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" s="5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B77" s="21" t="n">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -3632,19 +3472,19 @@
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" s="5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B78" s="21" t="n">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -3665,24 +3505,24 @@
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="5" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B79" s="21" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
@@ -3698,19 +3538,19 @@
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B80" s="21" t="n">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -3720,7 +3560,7 @@
       </c>
       <c r="F80" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -3731,24 +3571,24 @@
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" s="5" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B81" s="21" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F81" s="21" t="inlineStr">
@@ -3764,19 +3604,19 @@
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" s="5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B82" s="21" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3797,24 +3637,24 @@
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" s="5" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B83" s="21" t="n">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
@@ -3830,19 +3670,19 @@
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" s="5" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B84" s="21" t="n">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -3863,19 +3703,19 @@
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" s="5" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B85" s="21" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -3896,19 +3736,19 @@
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" s="5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B86" s="21" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -3929,19 +3769,19 @@
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" s="5" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B87" s="21" t="n">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -3956,25 +3796,25 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部回答済</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B88" s="21" t="n">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
@@ -3995,19 +3835,19 @@
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B89" s="21" t="n">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -4028,29 +3868,29 @@
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B90" s="21" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4061,19 +3901,19 @@
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B91" s="21" t="n">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -4083,7 +3923,7 @@
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -4094,29 +3934,29 @@
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B92" s="21" t="n">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>混合型特定施設の必要利用定員総数を定めるか</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F92" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -4127,29 +3967,29 @@
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="B93" s="21" t="n">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -4160,29 +4000,29 @@
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B94" s="21" t="n">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F94" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4193,19 +4033,19 @@
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B95" s="21" t="n">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
@@ -4215,7 +4055,7 @@
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -4226,19 +4066,19 @@
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" s="5" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B96" s="21" t="n">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
@@ -4248,7 +4088,7 @@
       </c>
       <c r="F96" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -4259,19 +4099,19 @@
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B97" s="21" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
@@ -4281,7 +4121,7 @@
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -4292,19 +4132,19 @@
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B98" s="21" t="n">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
@@ -4314,7 +4154,7 @@
       </c>
       <c r="F98" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -4325,29 +4165,29 @@
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B99" s="21" t="n">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -4358,19 +4198,19 @@
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" s="5" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B100" s="21" t="n">
-        <v>36</v>
+        <v>142</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -4380,7 +4220,7 @@
       </c>
       <c r="F100" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -4391,19 +4231,19 @@
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" s="5" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B101" s="21" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -4413,7 +4253,7 @@
       </c>
       <c r="F101" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
@@ -4424,19 +4264,19 @@
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" s="5" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B102" s="21" t="n">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -4446,7 +4286,7 @@
       </c>
       <c r="F102" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -4457,29 +4297,29 @@
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" s="5" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B103" s="21" t="n">
-        <v>84</v>
+        <v>147</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
@@ -4490,19 +4330,19 @@
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" s="5" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B104" s="21" t="n">
-        <v>86</v>
+        <v>149</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -4512,7 +4352,7 @@
       </c>
       <c r="F104" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -4523,19 +4363,19 @@
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" s="5" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B105" s="21" t="n">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -4545,7 +4385,7 @@
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
@@ -4556,24 +4396,24 @@
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" s="5" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B106" s="21" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F106" s="21" t="inlineStr">
@@ -4589,24 +4429,24 @@
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" s="5" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B107" s="21" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F107" s="21" t="inlineStr">
@@ -4622,19 +4462,19 @@
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" s="5" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B108" s="21" t="n">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -4655,24 +4495,24 @@
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" s="5" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B109" s="21" t="n">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
@@ -4688,19 +4528,19 @@
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" s="5" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B110" s="21" t="n">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -4721,19 +4561,19 @@
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" s="5" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B111" s="21" t="n">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
@@ -4754,19 +4594,19 @@
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" s="5" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B112" s="21" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
@@ -4787,24 +4627,24 @@
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" s="5" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B113" s="21" t="n">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F113" s="21" t="inlineStr">
@@ -4820,19 +4660,19 @@
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" s="5" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B114" s="21" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -4853,24 +4693,24 @@
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" s="5" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="B115" s="21" t="n">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F115" s="21" t="inlineStr">
@@ -4886,24 +4726,24 @@
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" s="5" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B116" s="21" t="n">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F116" s="21" t="inlineStr">
@@ -4919,24 +4759,24 @@
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" s="5" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B117" s="21" t="n">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F117" s="21" t="inlineStr">
@@ -4952,24 +4792,24 @@
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B118" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="B118" s="21" t="n">
-        <v>120</v>
-      </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F118" s="21" t="inlineStr">
@@ -4985,24 +4825,24 @@
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" s="5" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B119" s="21" t="n">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F119" s="21" t="inlineStr">
@@ -5018,19 +4858,19 @@
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" s="5" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="B120" s="21" t="n">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -5051,19 +4891,19 @@
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" s="5" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="B121" s="21" t="n">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
@@ -5084,24 +4924,24 @@
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" s="5" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="B122" s="21" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F122" s="21" t="inlineStr">
@@ -5117,24 +4957,24 @@
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" s="5" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B123" s="21" t="n">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F123" s="21" t="inlineStr">
@@ -5150,19 +4990,19 @@
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" s="5" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B124" s="21" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -5183,19 +5023,19 @@
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" s="5" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B125" s="21" t="n">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -5210,30 +5050,30 @@
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" s="5" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B126" s="21" t="n">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F126" s="21" t="inlineStr">
@@ -5249,19 +5089,19 @@
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" s="5" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B127" s="21" t="n">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -5282,19 +5122,19 @@
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" s="5" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B128" s="21" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -5309,30 +5149,30 @@
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" s="5" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B129" s="21" t="n">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F129" s="21" t="inlineStr">
@@ -5348,19 +5188,19 @@
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" s="5" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B130" s="21" t="n">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -5375,48 +5215,576 @@
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>一部解消</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B131" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B132" s="21" t="n">
+        <v>115</v>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月新設の3区分を0として立てる</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F132" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B133" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B134" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F134" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B135" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B136" s="21" t="n">
+        <v>127</v>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F136" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B137" s="21" t="n">
+        <v>128</v>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値を編集するか</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B138" s="21" t="n">
+        <v>129</v>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの利用率等の伸びの選択</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F138" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B139" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B140" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F140" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B141" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>一部確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B142" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F142" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B143" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B144" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B145" s="21" t="n">
+        <v>164</v>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B146" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F146" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>一部解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B131" s="21" t="n">
+      <c r="B147" s="21" t="n">
         <v>174</v>
       </c>
-      <c r="C131" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
-      <c r="D131" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F131" s="21" t="inlineStr">
+      <c r="F147" s="21" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
+      <c r="G147" s="6" t="inlineStr">
         <is>
           <t>未回答</t>
         </is>
       </c>
     </row>
-    <row r="132"/>
-    <row r="133" ht="48" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>注1）仮置きにより計画素案へ反映した事項は46件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
+    <row r="148"/>
+    <row r="149" ht="48" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>注1）仮置きにより計画素案へ反映した事項は62件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
 注3）未決164件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
@@ -5424,11 +5792,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A149:G149"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A133:G133"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6194,7 +6562,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>46件／台帳にないもの なし</t>
+          <t>62件／台帳にないもの なし</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>仮置きにより計画素案へ反映した62件と、令和8年10月30日までに決着をいただきたい事項。</t>
+          <t>仮置きにより計画素案へ反映した164件と、令和8年10月30日までに決着をいただきたい事項。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3198,2593 +3198,4939 @@
       <c r="F67" s="6" t="inlineStr"/>
       <c r="G67" s="6" t="inlineStr"/>
     </row>
-    <row r="68"/>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>決着しない場合の受託者の扱い</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>宛先</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="21" t="inlineStr">
+        <is>
+          <t>No.30</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>要介護度の構成は施設に入所している方と在宅の方を分けずに置き、入所の状況による重度化の見え方の違いを分けて算定していない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="21" t="inlineStr">
+        <is>
+          <t>No.34</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>第6章第6節5</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>第9段階の割合1.630が国の標準1.700を下回ることと、設定の経緯を確認できていないため第9期の条例の割合をそのまま用いていることを注に明示した</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="6" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="21" t="inlineStr">
+        <is>
+          <t>No.35</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率の比較は計画本文に掲げていない（保険料基準額の管内比較は北海道の公表資料により掲げている）</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr"/>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B71" s="21" t="n">
-        <v>40</v>
+        <v>66</v>
+      </c>
+      <c r="B71" s="21" t="inlineStr">
+        <is>
+          <t>No.36</t>
+        </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>第6章第6節5</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F71" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>所得段階別の第1号被保険者数は令和6年度の実績の構成比を固定し、予定収納率は所得段階別の実績を確認できていないため全段階一律99.0％としている旨を明示した</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr"/>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B72" s="21" t="n">
-        <v>50</v>
+        <v>67</v>
+      </c>
+      <c r="B72" s="21" t="inlineStr">
+        <is>
+          <t>No.115</t>
+        </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F72" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>令和9年4月1日に新設される3区分は実績がないため0として立て、国の様式の確定後に区分を改めることを注に明示した</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr"/>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="21" t="n">
-        <v>52</v>
+        <v>68</v>
+      </c>
+      <c r="B73" s="21" t="inlineStr">
+        <is>
+          <t>No.124</t>
+        </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F73" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>施設及び居住系サービスについても在宅と同じく令和7年度の要介護度別の利用率を固定し、これらに固有の伸びを別に選んでいない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B74" s="21" t="n">
-        <v>53</v>
+        <v>69</v>
+      </c>
+      <c r="B74" s="21" t="inlineStr">
+        <is>
+          <t>No.140</t>
+        </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>第2章第5節・第4章第3節</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F74" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合として用いることはできない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B75" s="21" t="n">
-        <v>63</v>
+        <v>70</v>
+      </c>
+      <c r="B75" s="21" t="inlineStr">
+        <is>
+          <t>No.149</t>
+        </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>第1章第2節・第8節</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F75" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認知症基本法の条文を受領していないため、計画素案には条番号のみを書き項番号は書いていない</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="21" t="n">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="B76" s="21" t="inlineStr">
+        <is>
+          <t>No.1</t>
+        </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>第1章第9節1</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>特別地域加算の対象地域の告示を確認できていないため、特定地域の基準①に該当するかどうかの判定は行わず［要確認］のまま残した</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="21" t="n">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="B77" s="21" t="inlineStr">
+        <is>
+          <t>No.3</t>
+        </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>第2章第2節1</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F77" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>類似保険者との比較は全国・北海道・上川管内21保険者及び健康とくらしの調査の同規模保険者40団体によることとし、給付・供給面の選定条件は［要協議］のまま残した</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="21" t="n">
-        <v>68</v>
+        <v>73</v>
+      </c>
+      <c r="B78" s="21" t="inlineStr">
+        <is>
+          <t>No.4</t>
+        </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPI H07・H08・H12・H16は代理指標へ振り替え、振替後の定義・基準値・留意点を掲げた</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B79" s="21" t="n">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="B79" s="21" t="inlineStr">
+        <is>
+          <t>No.5</t>
+        </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>第3章第2節</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>発注者・美瑛町</t>
-        </is>
-      </c>
-      <c r="F79" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>第9期の施策・事業実績の提供を受けられない間は、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B80" s="21" t="n">
-        <v>82</v>
+        <v>75</v>
+      </c>
+      <c r="B80" s="21" t="inlineStr">
+        <is>
+          <t>No.6</t>
+        </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>第3章第4節</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>R8.9.24</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>得点が0である項目について、取組がないのか要件を満たさないのか報告していないのかは公表資料から判別できない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr"/>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B81" s="21" t="n">
-        <v>88</v>
+        <v>76</v>
+      </c>
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>No.8</t>
+        </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>第2章第5節</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F81" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>3調査の点検事項（母数・回答の偏り・重複・未回答施設）の取扱いは当方の判定のままとし、確定していないものは［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr"/>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B82" s="21" t="n">
-        <v>95</v>
+        <v>77</v>
+      </c>
+      <c r="B82" s="21" t="inlineStr">
+        <is>
+          <t>No.19</t>
+        </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>第1章第5節</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F82" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>意見公募手続は令和9年1月にウェブサイトにより2週間実施し概要版を併せて示すものとして掲げ、方法及び時期は［要協議］のまま残した</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B83" s="21" t="n">
-        <v>96</v>
+        <v>78</v>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>No.42</t>
+        </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F83" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>キックオフ会議資料の工程表は現行のまま進めた</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B84" s="21" t="n">
-        <v>98</v>
+        <v>79</v>
+      </c>
+      <c r="B84" s="21" t="inlineStr">
+        <is>
+          <t>No.9</t>
+        </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>現に収録している対象者の範囲及び回収率によることとし、設問ごとに分母が異なることを注に明示した</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr"/>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B85" s="21" t="n">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>No.10</t>
+        </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>第2章第6節・第4章第3節</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F85" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）によることとし、代表KPI H14は各年9月30日現在の在籍者数を確認できないため未算定のままとした</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr"/>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B86" s="21" t="n">
-        <v>101</v>
+        <v>81</v>
+      </c>
+      <c r="B86" s="21" t="inlineStr">
+        <is>
+          <t>No.11</t>
+        </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>第2章第1節</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F86" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>町別・年齢4区分別の人口は令和5年までの各年10月1日現在の値であり、令和6年以降の趨勢は公表されている各年1月1日現在の値による（時点が9か月異なるため同じ系列としてつなげていない）旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B87" s="21" t="n">
-        <v>102</v>
+        <v>82</v>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>No.12</t>
+        </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>第1章第7節</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F87" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>一部回答済</t>
-        </is>
-      </c>
+          <t>基盤整備単位は3町（3圏域）とする案のままとし、圏域別の値は第9期計画による令和5年10月1日現在であること及び小学校区と6圏域の対応が確定していないことを注に明示した</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B88" s="21" t="n">
-        <v>103</v>
+        <v>83</v>
+      </c>
+      <c r="B88" s="21" t="inlineStr">
+        <is>
+          <t>No.18</t>
+        </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F88" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>骨子案は提出した内容のままとした</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr"/>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B89" s="21" t="n">
-        <v>105</v>
+        <v>84</v>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>No.22</t>
+        </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>第1章第6節・第8節</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F89" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>北海道の評価指標のうち市町村数を単位とするものの読替えは当方の整理によることとし（読替えの方法は第8節の表）、考え方が示された場合は改める旨を第6節の注に明示した</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr"/>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B90" s="21" t="n">
-        <v>106</v>
+        <v>85</v>
+      </c>
+      <c r="B90" s="21" t="inlineStr">
+        <is>
+          <t>No.27</t>
+        </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F90" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>前回との比較は第9期計画の本文に掲げられた指標に限り、検定は有効回答数を約4,700として行っている旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr"/>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B91" s="21" t="n">
-        <v>107</v>
+        <v>86</v>
+      </c>
+      <c r="B91" s="21" t="inlineStr">
+        <is>
+          <t>No.28</t>
+        </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F91" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>健康とくらしの調査の対象者に要支援者及び要介護者を含まないことと、他の調査と母集団が異なるため合算できないことを明示した</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr"/>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B92" s="21" t="n">
-        <v>113</v>
+        <v>87</v>
+      </c>
+      <c r="B92" s="21" t="inlineStr">
+        <is>
+          <t>No.38</t>
+        </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>第3章第4節</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="F92" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>公表されている全国集計の値によることとし、令和6年度分の評価は第8期の取組を反映したものであって評価の年度と取組の年度が一致しないことを注に明示した</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr"/>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr"/>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B93" s="21" t="n">
-        <v>123</v>
+        <v>88</v>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>No.46</t>
+        </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F93" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>令和8年9月25日の再提供により決着した。再提供を受けたファイルの値（3町合計と要介護度別まで円単位一致）による</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr"/>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B94" s="21" t="n">
-        <v>124</v>
+        <v>89</v>
+      </c>
+      <c r="B94" s="21" t="inlineStr">
+        <is>
+          <t>No.47</t>
+        </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>第6章第3節</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F94" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>給付費の実績は年報及び総括表詳細（保険者単位）によることとし、計画作成支援ツールの実績値は3町を合計しても保険者単位にならないため比較のためにのみ用いる旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B95" s="21" t="n">
-        <v>126</v>
+        <v>90</v>
+      </c>
+      <c r="B95" s="21" t="inlineStr">
+        <is>
+          <t>No.48</t>
+        </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>第3章第1節・第2節</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F95" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値によることとし、参加率の分母が見える化システムのA系列であり住民基本台帳とは異なる旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr"/>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B96" s="21" t="n">
-        <v>131</v>
+        <v>91</v>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>No.50</t>
+        </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>第3章第1節・第6章第6節</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F96" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>受領済みの年報・月報の値によることとし、重度要介護認定率の実績は見える化システムの系列による6.3％であって年報から算定すると6.38％になること（判定は変わらない）を注に明示した</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr"/>
+      <c r="F96" s="6" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr"/>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B97" s="21" t="n">
-        <v>132</v>
+        <v>92</v>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
+        <is>
+          <t>No.51</t>
+        </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F97" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>月報の値の接続のずれは受領点検に記録として残し、計画本文には用いていない</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr"/>
+      <c r="F97" s="6" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr"/>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B98" s="21" t="n">
-        <v>137</v>
+        <v>93</v>
+      </c>
+      <c r="B98" s="21" t="inlineStr">
+        <is>
+          <t>No.52</t>
+        </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>第3章第2節</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F98" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>区分の名称及び科目は令和6年度決算書の表記によることとし、「一般介護予防事業費」の項がないことを注に明示した（地域支援事業費の総額は変わらない）</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr"/>
+      <c r="F98" s="6" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr"/>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B99" s="21" t="n">
-        <v>141</v>
+        <v>94</v>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
+        <is>
+          <t>No.53</t>
+        </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>第6章第6節</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F99" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>財政調整基金を取り崩さないものとして算定し（不足する側に誤らない置き方）、1億円を取り崩した場合の月額への効きを併記した</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr"/>
+      <c r="F99" s="6" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr"/>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B100" s="21" t="n">
-        <v>142</v>
+        <v>95</v>
+      </c>
+      <c r="B100" s="21" t="inlineStr">
+        <is>
+          <t>No.54</t>
+        </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F100" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>中間報告会議議事録の文書プロパティの作成者を法人名とし、個人名が入らない形で再出力した</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr"/>
+      <c r="F100" s="6" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr"/>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B101" s="21" t="n">
-        <v>145</v>
+        <v>96</v>
+      </c>
+      <c r="B101" s="21" t="inlineStr">
+        <is>
+          <t>No.55</t>
+        </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F101" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>議事録の表記に関するご提案3件（文のねじれ・並列の「及び」・文体）を本文へ反映した。受領版の表記のままとするご判断であれば戻す</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr"/>
+      <c r="F101" s="6" t="inlineStr"/>
+      <c r="G101" s="6" t="inlineStr"/>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B102" s="21" t="n">
-        <v>146</v>
+        <v>97</v>
+      </c>
+      <c r="B102" s="21" t="inlineStr">
+        <is>
+          <t>No.56</t>
+        </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F102" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>他団体の要介護認定集計帳票6件は成果品に用いず、計画素案その他の成果品に当該団体名は現れない</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr"/>
+      <c r="F102" s="6" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr"/>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B103" s="21" t="n">
-        <v>147</v>
+        <v>98</v>
+      </c>
+      <c r="B103" s="21" t="inlineStr">
+        <is>
+          <t>No.59</t>
+        </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>第6章第6節4</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F103" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>調整交付金の算定基礎は標準給付費見込額と介護予防・日常生活支援総合事業費の合計であり包括的支援事業費及び任意事業費を含まないこと、この扱いにより第9期の公表値と一致することを注に明示した</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr"/>
+      <c r="F103" s="6" t="inlineStr"/>
+      <c r="G103" s="6" t="inlineStr"/>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B104" s="21" t="n">
-        <v>149</v>
+        <v>99</v>
+      </c>
+      <c r="B104" s="21" t="inlineStr">
+        <is>
+          <t>No.61</t>
+        </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとし、計画本文には掲げていない（第9期施策別評価表による）</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr"/>
+      <c r="F104" s="6" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr"/>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B105" s="21" t="n">
-        <v>151</v>
+        <v>100</v>
+      </c>
+      <c r="B105" s="21" t="inlineStr">
+        <is>
+          <t>No.80</t>
+        </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>第2章第6節</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>重複の判別は職員個票の突合によらず当該事業所への照会により行う（個人情報を保管しない方針による）旨を明示した</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr"/>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B106" s="21" t="n">
-        <v>2</v>
+        <v>101</v>
+      </c>
+      <c r="B106" s="21" t="inlineStr">
+        <is>
+          <t>No.83</t>
+        </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで資料を整えた</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr"/>
+      <c r="F106" s="6" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr"/>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B107" s="21" t="n">
-        <v>14</v>
+        <v>102</v>
+      </c>
+      <c r="B107" s="21" t="inlineStr">
+        <is>
+          <t>No.85</t>
+        </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F107" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>町別データシートは現行の内容のまま配付する</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr"/>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B108" s="21" t="n">
-        <v>15</v>
+        <v>103</v>
+      </c>
+      <c r="B108" s="21" t="inlineStr">
+        <is>
+          <t>No.60</t>
+        </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F108" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>単価を令和7年度で固定し、施策反映・給付適正化・基金取崩しを織り込まない置き方であり、算定上の月額基準額は低い側の水準にあることを明示した</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr"/>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B109" s="21" t="n">
-        <v>20</v>
+        <v>104</v>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
+        <is>
+          <t>No.64</t>
+        </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>公表版 参考（介護サービスの内容）</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>区域内に事業所がないサービスも区域外の事業所を利用できること、通常の事業の実施地域の外では実費の負担が生じることがあることを住民向けの記載に加えた</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr"/>
+      <c r="F109" s="6" t="inlineStr"/>
+      <c r="G109" s="6" t="inlineStr"/>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B110" s="21" t="n">
-        <v>23</v>
+        <v>105</v>
+      </c>
+      <c r="B110" s="21" t="inlineStr">
+        <is>
+          <t>No.69</t>
+        </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>第3章第4節</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F110" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>成果指向型配分枠は構成3町の回答の状況を確認できていないため第10期の施策に位置づけず、確認できた時点で判断する旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr"/>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B111" s="21" t="n">
-        <v>29</v>
+        <v>106</v>
+      </c>
+      <c r="B111" s="21" t="inlineStr">
+        <is>
+          <t>No.89</t>
+        </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>第1章第9節2</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F111" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr"/>
+      <c r="F111" s="6" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr"/>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B112" s="21" t="n">
-        <v>30</v>
+        <v>107</v>
+      </c>
+      <c r="B112" s="21" t="inlineStr">
+        <is>
+          <t>No.117</t>
+        </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F112" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す現行の方針のままとした</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr"/>
+      <c r="F112" s="6" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr"/>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B113" s="21" t="n">
-        <v>31</v>
+        <v>108</v>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>No.138</t>
+        </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F113" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ入力案とした</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr"/>
+      <c r="F113" s="6" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr"/>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B114" s="21" t="n">
-        <v>34</v>
+        <v>109</v>
+      </c>
+      <c r="B114" s="21" t="inlineStr">
+        <is>
+          <t>No.139</t>
+        </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F114" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>健康とくらしの調査の個票の再提供は依頼しない（成果品は収録済みで内容が確定しており不足がない）</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr"/>
+      <c r="F114" s="6" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr"/>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B115" s="21" t="n">
-        <v>35</v>
+        <v>110</v>
+      </c>
+      <c r="B115" s="21" t="inlineStr">
+        <is>
+          <t>No.148</t>
+        </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="F115" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>受領済みの画面の写しの範囲で入力値を示し、操作手引により確認できていない項目はその旨を明記した</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr"/>
+      <c r="F115" s="6" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr"/>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B116" s="21" t="n">
-        <v>36</v>
+        <v>111</v>
+      </c>
+      <c r="B116" s="21" t="inlineStr">
+        <is>
+          <t>No.90</t>
+        </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F116" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>前回調査との比較は割合のみとし、指標別の分母を第9期計画の本文から確認できない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr"/>
+      <c r="F116" s="6" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr"/>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B117" s="21" t="n">
-        <v>60</v>
+        <v>112</v>
+      </c>
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>No.91</t>
+        </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>第5章 基本目標5</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F117" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>給付実績の活用による確認等及び介護給付費通知は、実施の状況を確認したうえで第10期の実施の方針を定めることとし、現行の取組のまま位置づけた</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr"/>
+      <c r="F117" s="6" t="inlineStr"/>
+      <c r="G117" s="6" t="inlineStr"/>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B118" s="21" t="n">
-        <v>64</v>
+        <v>113</v>
+      </c>
+      <c r="B118" s="21" t="inlineStr">
+        <is>
+          <t>No.92</t>
+        </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>第5章 基本目標5</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F118" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認定調査の点検件数は、指定居宅介護支援事業所等への委託の状況を確認したうえで定める旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr"/>
+      <c r="F118" s="6" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr"/>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B119" s="21" t="n">
-        <v>84</v>
+        <v>114</v>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>No.97</t>
+        </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>第1章第9節1</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>発注者・東川町</t>
-        </is>
-      </c>
-      <c r="F119" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>条例の対応規定を確認していないため、省令の定めと対象事業所数（協力医療機関10事業所・生産性向上の取組に係る委員会15事業所）を示すにとどめた</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr"/>
+      <c r="F119" s="6" t="inlineStr"/>
+      <c r="G119" s="6" t="inlineStr"/>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B120" s="21" t="n">
-        <v>86</v>
+        <v>115</v>
+      </c>
+      <c r="B120" s="21" t="inlineStr">
+        <is>
+          <t>No.99</t>
+        </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F120" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>過疎地域における小規模多機能型居宅介護の登録定員の超過の特例を用いずに見込量を算定している旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr"/>
+      <c r="F120" s="6" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr"/>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B121" s="21" t="n">
-        <v>89</v>
+        <v>116</v>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>No.108</t>
+        </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F121" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>補正を行っても開きが残る6種別は趨勢の置き方によるものではなく供給の状況又は制度の区分によるものであり、第4節の整備方針及び確保方策において扱う旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr"/>
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B122" s="21" t="n">
-        <v>93</v>
+        <v>117</v>
+      </c>
+      <c r="B122" s="21" t="inlineStr">
+        <is>
+          <t>No.111</t>
+        </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="F122" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>趨勢に現れない要因は給付費を増やす向きか減らす向きかを記すにとどめ、数値には織り込んでいない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr"/>
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B123" s="21" t="n">
-        <v>97</v>
+        <v>118</v>
+      </c>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>No.118</t>
+        </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>第5章 基本目標1</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F123" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>地域ケア会議の指標に施策化への転換率を加え、令和9年度に基準値を把握し令和10年度から目標値を置くこと、率とともに実数を併記すること、記録は3町が作成し集計値を提出することを明示した</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr"/>
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B124" s="21" t="n">
-        <v>99</v>
+        <v>119</v>
+      </c>
+      <c r="B124" s="21" t="inlineStr">
+        <is>
+          <t>No.119</t>
+        </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>第5章 基本目標1</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F124" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>3町共通の記録様式は令和9年度に整えることとし、様式そのものは協議資料にとどめた</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr"/>
+      <c r="F124" s="6" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr"/>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B125" s="21" t="n">
-        <v>104</v>
+        <v>120</v>
+      </c>
+      <c r="B125" s="21" t="inlineStr">
+        <is>
+          <t>No.120</t>
+        </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>第5章 基本目標1</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F125" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>件数は地域ケア個別会議と地域ケア推進会議を分けずに計数する旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr"/>
+      <c r="F125" s="6" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr"/>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B126" s="21" t="n">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="B126" s="21" t="inlineStr">
+        <is>
+          <t>No.121</t>
+        </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>第5章 基本目標1</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F126" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>3町の実績は令和7年度の地域包括支援センター事業実施報告書により把握できる範囲で記述し、計数の単位が町により異なるため3町を合計できない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr"/>
+      <c r="F126" s="6" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B127" s="21" t="n">
-        <v>109</v>
+        <v>122</v>
+      </c>
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>No.125</t>
+        </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F127" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認定率は年報（各年度末現在）によることとし、総括表（各年9月末現在）及び将来推計の参考シートの値との違いが時点等によるものである旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr"/>
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr"/>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B128" s="21" t="n">
-        <v>110</v>
+        <v>123</v>
+      </c>
+      <c r="B128" s="21" t="inlineStr">
+        <is>
+          <t>No.127</t>
+        </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F128" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>人口の基礎は案C（地方創生総合戦略と住民基本台帳の実績趨勢）により、社人研の推計による場合との差を対比して掲げた</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr"/>
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B129" s="21" t="n">
-        <v>111</v>
+        <v>124</v>
+      </c>
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t>No.133</t>
+        </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F129" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>介護老人保健施設の令和8年度（4か月）の減少を将来へ延長していない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr"/>
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B130" s="21" t="n">
-        <v>112</v>
+        <v>125</v>
+      </c>
+      <c r="B130" s="21" t="inlineStr">
+        <is>
+          <t>No.136</t>
+        </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F130" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>実績は年報（保険者単位）によることとし、見える化システムの画面が表示する令和7年度の値と一部の区分で食い違う旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr"/>
+      <c r="F130" s="6" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr"/>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B131" s="21" t="n">
-        <v>114</v>
+        <v>126</v>
+      </c>
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t>No.143</t>
+        </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>資料7</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F131" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとし、記号の意味と解消の方法を資料7に掲げた</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr"/>
+      <c r="F131" s="6" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr"/>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B132" s="21" t="n">
-        <v>115</v>
+        <v>127</v>
+      </c>
+      <c r="B132" s="21" t="inlineStr">
+        <is>
+          <t>No.154</t>
+        </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F132" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>町別の図は計画素案 第2章第1節に加えず、協議用の資料にとどめた</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr"/>
+      <c r="F132" s="6" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr"/>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B133" s="21" t="n">
-        <v>116</v>
+        <v>128</v>
+      </c>
+      <c r="B133" s="21" t="inlineStr">
+        <is>
+          <t>No.157</t>
+        </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F133" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとした</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr"/>
+      <c r="F133" s="6" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr"/>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B134" s="21" t="n">
-        <v>120</v>
+        <v>129</v>
+      </c>
+      <c r="B134" s="21" t="inlineStr">
+        <is>
+          <t>No.158</t>
+        </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F134" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>代表KPI H06・H12の分母を設問ごとの有効回答とし、町別の値は掲げていない</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr"/>
+      <c r="F134" s="6" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr"/>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B135" s="21" t="n">
-        <v>125</v>
+        <v>130</v>
+      </c>
+      <c r="B135" s="21" t="inlineStr">
+        <is>
+          <t>No.159</t>
+        </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F135" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>通いの場の目標値は現在の実施の状況を前提として置き、整備が進む町がある場合は中間年の見直しで改める旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr"/>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr"/>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B136" s="21" t="n">
-        <v>127</v>
+        <v>131</v>
+      </c>
+      <c r="B136" s="21" t="inlineStr">
+        <is>
+          <t>No.160</t>
+        </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F136" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>認知症サポーターの養成は現に確認できる取組の範囲で掲げ、養成人数の目標値を置いていない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr"/>
+      <c r="F136" s="6" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr"/>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B137" s="21" t="n">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t>No.161</t>
+        </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F137" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>チームオレンジは東川町の取組として掲げ、他の町への展開は3町と協議して定める旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr"/>
+      <c r="F137" s="6" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr"/>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B138" s="21" t="n">
-        <v>129</v>
+        <v>133</v>
+      </c>
+      <c r="B138" s="21" t="inlineStr">
+        <is>
+          <t>No.162</t>
+        </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F138" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>美瑛町の認知症初期集中支援推進事業は令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残した</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr"/>
+      <c r="F138" s="6" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr"/>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B139" s="21" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>No.163</t>
+        </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>第3章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F139" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G139" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>地域リハビリテーション活動支援事業は美瑛町の取組として記述し、3町展開とは書かないことに改めた</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr"/>
+      <c r="F139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr"/>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B140" s="21" t="n">
-        <v>136</v>
+        <v>135</v>
+      </c>
+      <c r="B140" s="21" t="inlineStr">
+        <is>
+          <t>No.16</t>
+        </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F140" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>保険料算定の前提は単価固定・施策反映なし・適正化を織り込まない・基金取崩しなしによることを明示した（No.60と同じ前提）</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr"/>
+      <c r="F140" s="6" t="inlineStr"/>
+      <c r="G140" s="6" t="inlineStr"/>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B141" s="21" t="n">
-        <v>150</v>
+        <v>136</v>
+      </c>
+      <c r="B141" s="21" t="inlineStr">
+        <is>
+          <t>No.164</t>
+        </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>第6章第4節4</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F141" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>一部確認済み</t>
-        </is>
-      </c>
+          <t>美瑛町の地域密着型介護老人福祉施設は現定員の据え置き案を掲げ、本文は［要協議］のまま残した</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr"/>
+      <c r="F141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr"/>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B142" s="21" t="n">
-        <v>152</v>
+        <v>137</v>
+      </c>
+      <c r="B142" s="21" t="inlineStr">
+        <is>
+          <t>No.165</t>
+        </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F142" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>難聴高齢者の早期発見・早期介入は令和8年度に新たに加えられた交付金の評価項目であり町により得点に差があることを示し、現に確認できる範囲で掲げるにとどめた</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr"/>
+      <c r="F142" s="6" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr"/>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B143" s="21" t="n">
-        <v>153</v>
+        <v>138</v>
+      </c>
+      <c r="B143" s="21" t="inlineStr">
+        <is>
+          <t>No.166</t>
+        </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F143" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>通いの場の目標値は令和6年度の水準が続くものとして置いた</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr"/>
+      <c r="F143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr"/>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B144" s="21" t="n">
-        <v>157</v>
+        <v>139</v>
+      </c>
+      <c r="B144" s="21" t="inlineStr">
+        <is>
+          <t>No.167</t>
+        </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F144" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr">
-        <is>
-          <t>対応中</t>
-        </is>
-      </c>
+          <t>認知症サポーター・ステップアップ講座は現に確認できる取組の範囲で記述し目標値を置いていない</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr"/>
+      <c r="F144" s="6" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr"/>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B145" s="21" t="n">
-        <v>164</v>
+        <v>140</v>
+      </c>
+      <c r="B145" s="21" t="inlineStr">
+        <is>
+          <t>No.170</t>
+        </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>発注者・美瑛町</t>
-        </is>
-      </c>
-      <c r="F145" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>計画素案から協議用の成果品へ移す8件を移し、「協議」判定の16件は素案に残した</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr"/>
+      <c r="F145" s="6" t="inlineStr"/>
+      <c r="G145" s="6" t="inlineStr"/>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B146" s="21" t="n">
-        <v>170</v>
+        <v>141</v>
+      </c>
+      <c r="B146" s="21" t="inlineStr">
+        <is>
+          <t>No.172</t>
+        </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F146" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr">
-        <is>
-          <t>一部解消</t>
-        </is>
-      </c>
+          <t>交付金の評価を示す図は計画本文に掲げず、策定委員会の資料にとどめた</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr"/>
+      <c r="F146" s="6" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr"/>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" s="21" t="inlineStr">
+        <is>
+          <t>No.174</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>人口及び第1号被保険者数は案Cにそろえ、見える化システムへの入力値も案Cによった</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr"/>
+      <c r="F147" s="6" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr"/>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" s="21" t="inlineStr">
+        <is>
+          <t>No.2</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>第1章第9節1</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向の表明は、基準及び手続が確定していないため行わないものとし、省令等の確定後に3町と協議して定める旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr"/>
+      <c r="F148" s="6" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149" s="21" t="inlineStr">
+        <is>
+          <t>No.13</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>第1章第7節</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域は、北海道の指定事業所一覧の「通常の事業の実施地域」により判定することとした</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr"/>
+      <c r="F149" s="6" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr"/>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150" s="21" t="inlineStr">
+        <is>
+          <t>No.14</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>人口推計の基礎は案C（総合戦略と住民基本台帳の実績趨勢）による</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr"/>
+      <c r="F150" s="6" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr"/>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>No.15</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>認定者数は年報の年度末現在を基準とし、月次推移は計画本文に掲げていない</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr"/>
+      <c r="F151" s="6" t="inlineStr"/>
+      <c r="G151" s="6" t="inlineStr"/>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152" s="21" t="inlineStr">
+        <is>
+          <t>No.17</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>資料2</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めず、役割分担と共通KPIにより接続することとした</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr"/>
+      <c r="F152" s="6" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr"/>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153" s="21" t="inlineStr">
+        <is>
+          <t>No.20</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>第1章第8節</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>北海道の第9期支援計画の8基本目標との対応により整合を図った</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr"/>
+      <c r="F153" s="6" t="inlineStr"/>
+      <c r="G153" s="6" t="inlineStr"/>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154" s="21" t="inlineStr">
+        <is>
+          <t>No.21</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>成果品の仕様は仕様書の定めによる</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr"/>
+      <c r="F154" s="6" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr"/>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>No.23</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>第2章第3節6</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>事業所の定員は北海道の各名簿及び介護サービス情報公表システムによることとし、未確認のものは［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr"/>
+      <c r="F155" s="6" t="inlineStr"/>
+      <c r="G155" s="6" t="inlineStr"/>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B156" s="21" t="inlineStr">
+        <is>
+          <t>No.26</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>第5章 基本目標2・基本目標3</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>認知症・医療介護連携の実績は、交付金の評価結果及び3町の地域包括支援センター事業実施報告書の範囲で記述した</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr"/>
+      <c r="F156" s="6" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B157" s="21" t="inlineStr">
+        <is>
+          <t>No.29</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>第6章第1節</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定し、重度化は人口の高齢化による分のみを見込んだ</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr"/>
+      <c r="F157" s="6" t="inlineStr"/>
+      <c r="G157" s="6" t="inlineStr"/>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B158" s="21" t="inlineStr">
+        <is>
+          <t>No.31</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>第6章第6節2</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化による抑制を推計に織り込まず、対象サービスの割合と10％抑制の効きを併記した</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr"/>
+      <c r="F158" s="6" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159" s="21" t="inlineStr">
+        <is>
+          <t>No.74</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>第2章第3節6</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>家賃等の費用の水準は北海道における情報の収集を確認できないため把握しておらず、費用の面からの選択は扱っていない旨を注に明示した</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr"/>
+      <c r="F159" s="6" t="inlineStr"/>
+      <c r="G159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B160" s="21" t="inlineStr">
+        <is>
+          <t>No.144</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>統合した成果品の元の資料を残す</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr"/>
+      <c r="F160" s="6" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr"/>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B161" s="21" t="inlineStr">
+        <is>
+          <t>No.156</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別第1号被保険者数は当方の算定（16段階×8年度）により、所得段階の設定は弾力化を選ぶ</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr"/>
+      <c r="F161" s="6" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B162" s="21" t="inlineStr">
+        <is>
+          <t>No.169</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>第3章第2節・第5章 基本目標2</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけていない</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr"/>
+      <c r="F162" s="6" t="inlineStr"/>
+      <c r="G162" s="6" t="inlineStr"/>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B163" s="21" t="inlineStr">
+        <is>
+          <t>No.171</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B164" s="21" t="inlineStr">
+        <is>
+          <t>No.173</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>本文の図と別冊の図表集の対応は現行のままとした</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr"/>
+      <c r="F164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr"/>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B165" s="21" t="inlineStr">
+        <is>
+          <t>No.24</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>第6章第2節・第4節1</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せを行わなかった</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr"/>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B166" s="21" t="inlineStr">
+        <is>
+          <t>No.25</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>第4章第3節・第5章</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIのうち基準値のないものは令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置くこととした</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr"/>
+      <c r="F166" s="6" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B167" s="21" t="inlineStr">
+        <is>
+          <t>No.175</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>第1章第9節5・第5章 基本目標1・基本目標4</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>介護情報基盤の活用は本格運用開始日（令和10年4月1日）までに完了することを前提として記載し、年度ごとの事務の工程は［要確認］として残した。事業所への周知と登録の支援は広域連合・3町・事業者が担うものとして掲げた</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr"/>
+      <c r="F167" s="6" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B168" s="21" t="inlineStr">
+        <is>
+          <t>No.176</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>第1章第9節5・第5章 基本目標4</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス事業者経営情報データベースは活用の方針のみを記載し、数値は掲げていない。用いられる範囲を確認して用いる旨を［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr"/>
+      <c r="F168" s="6" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B169" s="21" t="inlineStr">
+        <is>
+          <t>No.177</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>第1章第9節5・第5章 基本目標3・基本目標4</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>都道府県との協定に基づく連携は北海道及び事業者とともに活用を検討する旨のみを記載し、市町村の役割が示された時点で関与の仕方を定めることとした</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr"/>
+      <c r="F169" s="6" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr"/>
+    </row>
+    <row r="170"/>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="4" t="inlineStr"/>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>決着しない場合の受託者の扱い</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>宛先</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B173" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B174" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>年報・月報の受領に伴う確認</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>受領済みの年報・月報の値による</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F174" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B175" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度決算書の受領に伴う確認</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B176" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F176" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B177" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F177" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B178" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>広域連合において行うべき事業の優先順位</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F178" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B179" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>算定方法の国の様式との整合（点検結果）</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F179" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B180" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F180" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B181" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>グループホームびえいの郷の定員減の時期</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>北海道の名簿の定員のまま概算する</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="F181" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B182" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F182" s="21" t="inlineStr">
+        <is>
+          <t>R8.9.24</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B183" s="21" t="n">
+        <v>88</v>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F183" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B184" s="21" t="n">
+        <v>95</v>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F184" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B185" s="21" t="n">
+        <v>96</v>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F185" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B186" s="21" t="n">
+        <v>98</v>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F186" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B187" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F187" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B188" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F188" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B189" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F189" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>一部回答済</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B190" s="21" t="n">
+        <v>103</v>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F190" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B191" s="21" t="n">
+        <v>105</v>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>施策反映を行わないまま概算する（安全側）</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F191" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B192" s="21" t="n">
+        <v>106</v>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F192" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B193" s="21" t="n">
+        <v>107</v>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F193" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B194" s="21" t="n">
+        <v>113</v>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F194" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B195" s="21" t="n">
+        <v>123</v>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F195" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B196" s="21" t="n">
+        <v>124</v>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F196" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B197" s="21" t="n">
+        <v>126</v>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>基本推計に近いP3で概算する</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F197" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B198" s="21" t="n">
+        <v>131</v>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F198" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B199" s="21" t="n">
+        <v>132</v>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F199" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B200" s="21" t="n">
+        <v>137</v>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F200" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B201" s="21" t="n">
+        <v>141</v>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>区域を越えた施設利用の扱い</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F201" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B202" s="21" t="n">
+        <v>142</v>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>第1次概算を既定値のまま出してよいか</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F202" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B203" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F203" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B204" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F204" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B205" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F205" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B206" s="21" t="n">
+        <v>149</v>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F206" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B207" s="21" t="n">
+        <v>151</v>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+        </is>
+      </c>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+        </is>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F207" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B208" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="F208" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B209" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>人口推計の基礎とする系列</t>
+        </is>
+      </c>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+        </is>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F209" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B210" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>認定者数の基準月と月次推移</t>
+        </is>
+      </c>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F210" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B211" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F211" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B212" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>事業所の定員・稼働率データ</t>
+        </is>
+      </c>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F212" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B213" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>重度化の速度の前提</t>
+        </is>
+      </c>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+        </is>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F213" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G213" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B214" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F214" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B215" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化の実施予定と推計での扱い</t>
+        </is>
+      </c>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F215" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B216" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>第9段階の乗率の経緯</t>
+        </is>
+      </c>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F216" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B217" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率</t>
+        </is>
+      </c>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+        </is>
+      </c>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F217" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G217" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B218" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別被保険者数の実績と収納率</t>
+        </is>
+      </c>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F218" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B219" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>第10期の保険料算定の前提（受託者案）</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+        </is>
+      </c>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F219" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B220" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
+        </is>
+      </c>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F220" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B221" s="21" t="n">
+        <v>84</v>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>東川町の施設整備・サービス提供方針</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>発注者・東川町</t>
+        </is>
+      </c>
+      <c r="F221" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G221" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B222" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F222" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G222" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B223" s="21" t="n">
+        <v>89</v>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F223" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G223" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B224" s="21" t="n">
+        <v>93</v>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+        </is>
+      </c>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F224" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B225" s="21" t="n">
+        <v>97</v>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月1日から義務となる2件への対応</t>
+        </is>
+      </c>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+        </is>
+      </c>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F225" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G225" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B226" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F226" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B227" s="21" t="n">
+        <v>104</v>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F227" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B228" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>補正しても外れるサービス6件の理由</t>
+        </is>
+      </c>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F228" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B229" s="21" t="n">
+        <v>109</v>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F229" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B230" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+        </is>
+      </c>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F230" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G230" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B231" s="21" t="n">
+        <v>111</v>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F231" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B232" s="21" t="n">
+        <v>112</v>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
+        </is>
+      </c>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F232" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G232" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B233" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F233" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B234" s="21" t="n">
+        <v>115</v>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+        </is>
+      </c>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月新設の3区分を0として立てる</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F234" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B235" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+        </is>
+      </c>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+        </is>
+      </c>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F235" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G235" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B236" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+        </is>
+      </c>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F236" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B237" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+        </is>
+      </c>
+      <c r="D237" s="6" t="inlineStr">
+        <is>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F237" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B238" s="21" t="n">
+        <v>127</v>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
+        <is>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F238" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B239" s="21" t="n">
+        <v>128</v>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の実績見込み値を編集するか</t>
+        </is>
+      </c>
+      <c r="D239" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F239" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B240" s="21" t="n">
+        <v>129</v>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの利用率等の伸びの選択</t>
+        </is>
+      </c>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F240" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B241" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+        </is>
+      </c>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F241" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B242" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
+        </is>
+      </c>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F242" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B243" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供</t>
+        </is>
+      </c>
+      <c r="D243" s="6" t="inlineStr">
+        <is>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+        </is>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F243" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
+          <t>一部確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B244" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+        </is>
+      </c>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F244" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B245" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="C245" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+        </is>
+      </c>
+      <c r="D245" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+        </is>
+      </c>
+      <c r="E245" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F245" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G245" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B246" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B247" s="21" t="n">
+        <v>164</v>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="F247" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G247" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B248" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F248" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G248" s="6" t="inlineStr">
+        <is>
+          <t>一部解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B147" s="21" t="n">
+      <c r="B249" s="21" t="n">
         <v>174</v>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C249" s="6" t="inlineStr">
         <is>
           <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="D249" s="6" t="inlineStr">
+        <is>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F147" s="21" t="inlineStr">
+      <c r="F249" s="21" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G147" s="6" t="inlineStr">
+      <c r="G249" s="6" t="inlineStr">
         <is>
           <t>未回答</t>
         </is>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149" ht="48" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>注1）仮置きにより計画素案へ反映した事項は62件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
+    <row r="250"/>
+    <row r="251" ht="48" customHeight="1">
+      <c r="A251" s="7" t="inlineStr">
+        <is>
+          <t>注1）仮置きにより計画素案へ反映した事項は164件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
 注3）未決164件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
@@ -5792,11 +8138,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A149:G149"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A69:G69"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A171:G171"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A251:G251"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6562,7 +8908,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>62件／台帳にないもの なし</t>
+          <t>164件／台帳にないもの なし</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決164件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決168件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <is>
           <t>注1）仮置きにより計画素案へ反映した事項は164件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決164件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+注3）未決168件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決168件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決171件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <is>
           <t>注1）仮置きにより計画素案へ反映した事項は164件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決168件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+注3）未決171件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決171件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決173件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <is>
           <t>注1）仮置きにより計画素案へ反映した事項は164件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決171件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+注3）未決173件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決173件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決172件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <is>
           <t>注1）仮置きにより計画素案へ反映した事項は164件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決173件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+注3）未決172件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>仮置きにより計画素案へ反映した164件と、令和8年10月30日までに決着をいただきたい事項。</t>
+          <t>仮置きにより計画素案へ反映した162件と、令和8年10月30日までに決着をいただきたい事項。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決172件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決173件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
         </is>
       </c>
     </row>
@@ -1801,17 +1801,17 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>No.113</t>
+          <t>No.131</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>第6章第4節4</t>
+          <t>第6章第2節・第3節2</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数は定めないこととした</t>
+          <t>利用回（日）数と、介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -1824,17 +1824,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>No.131</t>
+          <t>No.112</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節・第3節2</t>
+          <t>第6章第3節2</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>利用回（日）数と、介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた</t>
+          <t>令和6年度の利用者実人数を基礎として量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別に示した</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>No.112</t>
+          <t>No.106</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第6章第3節2</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を基礎として量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別に示した</t>
+          <t>サービス別の趨勢を反映する補正は行わず、補正した場合の月額への効きを併記した</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>No.106</t>
+          <t>No.105</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わず、補正した場合の月額への効きを併記した</t>
+          <t>施策による見込量の増減を織り込まなかった（自然体）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>No.105</t>
+          <t>No.137</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>施策による見込量の増減を織り込まなかった（自然体）</t>
+          <t>単価を令和7年度で固定し、実績の趨勢を織り込んだ場合の月額への効きを併記した</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>No.137</t>
+          <t>No.110</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定し、実績の趨勢を織り込んだ場合の月額への効きを併記した</t>
+          <t>給付の適正化による抑制を織り込まず、対象サービスの割合と10％抑制した場合の効きを併記した</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -1939,17 +1939,17 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>No.110</t>
+          <t>No.150</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第6章第3節2</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>給付の適正化による抑制を織り込まず、対象サービスの割合と10％抑制した場合の効きを併記した</t>
+          <t>量の見込みは掲げず、構成3町の認知症総合支援事業の実施状況を掲げた</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
@@ -1962,17 +1962,17 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>No.150</t>
+          <t>No.98</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>第6章第3節2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>量の見込みは掲げず、構成3町の認知症総合支援事業の実施状況を掲げた</t>
+          <t>省令上の類型は計画に掲げていない</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr"/>
@@ -1985,17 +1985,17 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>No.98</t>
+          <t>No.100</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第2節・第3節</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型は計画に掲げていない</t>
+          <t>令和7年度を基準年度とし、総括表の単価により要介護度別の伸びで算定した</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
@@ -2008,17 +2008,17 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>No.100</t>
+          <t>No.101</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節・第3節</t>
+          <t>第6章第2節・第6節2</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>令和7年度を基準年度とし、総括表の単価により要介護度別の伸びで算定した</t>
+          <t>第6章第2節の表は当方の算定による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げた</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
@@ -2031,17 +2031,17 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>No.101</t>
+          <t>No.103</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節・第6節2</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の表は当方の算定による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げた</t>
+          <t>令和8年度（4か月）を基準年度に用いず、季節による補正も行わない旨を注に明示した</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>No.103</t>
+          <t>No.107</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を基準年度に用いず、季節による補正も行わない旨を注に明示した</t>
+          <t>施設及び居住系サービスの定員の縮小の趨勢を将来へ延長しない旨を注に明示した</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
@@ -2077,17 +2077,17 @@
       </c>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t>No.107</t>
+          <t>No.141</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>第6章第4節4</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>施設及び居住系サービスの定員の縮小の趨勢を将来へ延長しない旨を注に明示した</t>
+          <t>必要利用定員総数は現に指定を受けている定員を基礎とするもので、第2節の見込量（当連合の被保険者の受給者数）とは数える対象が異なる旨を注に明示した</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -2100,17 +2100,17 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>No.141</t>
+          <t>No.146</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第6章第4節4</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は現に指定を受けている定員を基礎とするもので、第2節の見込量（当連合の被保険者の受給者数）とは数える対象が異なる旨を注に明示した</t>
+          <t>要介護度別の伸びによる算定を採り、一律の伸びによる値との差を併記した</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B21" s="21" t="inlineStr">
         <is>
-          <t>No.146</t>
+          <t>No.151</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定を採り、一律の伸びによる値との差を併記した</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設は、実績の減少が定員の縮小によるものであるため、補正を行う場合でも対象から外す扱いとする旨を明示した</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -2146,17 +2146,17 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>No.151</t>
+          <t>No.93</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第5章 基本目標5・第6章第6節4</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設は、実績の減少が定員の縮小によるものであるため、補正を行う場合でも対象から外す扱いとする旨を明示した</t>
+          <t>主要3事業の取組状況が調整交付金の算定に勘案されることと、本計画がその減額を織り込んでいないことを明示した</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>No.93</t>
+          <t>No.82</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標5・第6章第6節4</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>主要3事業の取組状況が調整交付金の算定に勘案されることと、本計画がその減額を織り込んでいないことを明示した</t>
+          <t>町別への按分は規約によるため算定できないものとして、構成町の一般会計繰入金は3町計の概算のみを示した</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -2192,17 +2192,17 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>No.82</t>
+          <t>No.123</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は規約によるため算定できないものとして、構成町の一般会計繰入金は3町計の概算のみを示した</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま、給付費の置き方の対比（③）として掲げた</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>No.123</t>
+          <t>No.126</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第6章第1節・第2節</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま、給付費の置き方の対比（③）として掲げた</t>
+          <t>年齢階級別の人口に階級別・要介護度別の認定率を乗じる方法（見える化システムの基本推計に近いもの）により算定した</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
@@ -2238,17 +2238,17 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>No.126</t>
+          <t>No.130</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節・第2節</t>
+          <t>第1章第2節・第8節・第5章 基本目標2・資料2</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>年齢階級別の人口に階級別・要介護度別の認定率を乗じる方法（見える化システムの基本推計に近いもの）により算定した</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画は構成3町がそれぞれ策定するものとして反映した</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
@@ -2261,17 +2261,17 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>No.130</t>
+          <t>No.104</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第1章第2節・第8節・第5章 基本目標2・資料2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画は構成3町がそれぞれ策定するものとして反映した</t>
+          <t>単価を令和7年度で固定し、令和8年度の水準（残差）に置いた場合の月額への効きを据え置きの一覧に示した</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
@@ -2284,17 +2284,17 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>No.104</t>
+          <t>No.109</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定し、令和8年度の水準（残差）に置いた場合の月額への効きを据え置きの一覧に示した</t>
+          <t>単価を令和7年度で固定し、実績の趨勢を置いた場合の月額への効きを併記した</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -2307,17 +2307,17 @@
       </c>
       <c r="B29" s="21" t="inlineStr">
         <is>
-          <t>No.109</t>
+          <t>No.114</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第6章第1節・第3節</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定し、実績の趨勢を置いた場合の月額への効きを併記した</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定した</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -2330,17 +2330,17 @@
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>No.114</t>
+          <t>No.132</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節・第3節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定した</t>
+          <t>在宅サービスの実績見込み値は当方の入力案のまま置いた</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B31" s="21" t="inlineStr">
         <is>
-          <t>No.132</t>
+          <t>No.142</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値は当方の入力案のまま置いた</t>
+          <t>ご決定をお待ちしている事項は既定値によって算定していることを算定の冒頭に明示した</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>No.142</t>
+          <t>No.145</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>ご決定をお待ちしている事項は既定値によって算定していることを算定の冒頭に明示した</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）により算定し、町別データシートは計画作成支援ツールの値のまま示したうえで、3町を足しても年報の値にならない旨を注記した</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>No.145</t>
+          <t>No.147</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）により算定し、町別データシートは計画作成支援ツールの値のまま示したうえで、3町を足しても年報の値にならない旨を注記した</t>
+          <t>見える化システムの伸びは令和8年度を含まない（令和6年度→令和7年度）を採ったものとして入力値を示した</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>No.147</t>
+          <t>No.84</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第4節4</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びは令和8年度を含まない（令和6年度→令和7年度）を採ったものとして入力値を示した</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残した</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>No.84</t>
+          <t>No.116</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第6章第4節4</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残した</t>
+          <t>供給の制約（人材）を見込量に反映せず、需要のみで算定した旨を注に明示した</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
@@ -2468,17 +2468,17 @@
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>No.116</t>
+          <t>No.152</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映せず、需要のみで算定した旨を注に明示した</t>
+          <t>町別の人口の将来推計は計画本文に掲げていない</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
@@ -2491,17 +2491,17 @@
       </c>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>No.152</t>
+          <t>No.153</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計は計画本文に掲げていない</t>
+          <t>人口の将来推計は案C（地方創生総合戦略と住民基本台帳の実績趨勢）によった</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
@@ -2514,17 +2514,17 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>No.153</t>
+          <t>No.7</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節・第6章第1節</t>
+          <t>第1章第6節</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計は案C（地方創生総合戦略と住民基本台帳の実績趨勢）によった</t>
+          <t>第9期の自己評価及び北海道への報告の実績は確認できないものとして、毎年度の自己評価の結果を策定委員会へ報告し北海道への報告にも用いることを置いた</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>No.7</t>
+          <t>No.86</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第1章第6節</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価及び北海道への報告の実績は確認できないものとして、毎年度の自己評価の結果を策定委員会へ報告し北海道への報告にも用いることを置いた</t>
+          <t>地域支援事業費（B）から交付金を財源とする2事業を除く方法により、保険料収納必要額からの控除は行わない旨（二重控除を避ける）を明示した</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
@@ -2560,17 +2560,17 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>No.86</t>
+          <t>No.94</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第1章第2節・第5章 基本目標5・資料5</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から交付金を財源とする2事業を除く方法により、保険料収納必要額からの控除は行わない旨（二重控除を避ける）を明示した</t>
+          <t>給付適正化計画は第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示した</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
@@ -2583,17 +2583,17 @@
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>No.94</t>
+          <t>No.128</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第1章第2節・第5章 基本目標5・資料5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画は第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示した</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないものとして入力値を示し、当方の算定（令和7年度基準）との差として残した</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>No.128</t>
+          <t>No.129</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないものとして入力値を示し、当方の算定（令和7年度基準）との差として残した</t>
+          <t>見える化システムの利用率等の伸びは令和8年度を含まない（令和6年度→令和7年度）を選んだものとして入力値を示した</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr"/>
@@ -2629,17 +2629,17 @@
       </c>
       <c r="B43" s="21" t="inlineStr">
         <is>
-          <t>No.129</t>
+          <t>No.33</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びは令和8年度を含まない（令和6年度→令和7年度）を選んだものとして入力値を示した</t>
+          <t>所得段階は第9期の条例による16段階と公費による軽減前の割合を据え置いて算定し、政令の公布後に再算定する旨を明示した</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr"/>
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B44" s="21" t="inlineStr">
         <is>
-          <t>No.33</t>
+          <t>No.39</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節</t>
+          <t>第4章第3節</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>所得段階は第9期の条例による16段階と公費による軽減前の割合を据え置いて算定し、政令の公布後に再算定する旨を明示した</t>
+          <t>代表KPIは第9期計画の目標指標を引き継ぎ、別の指標を新たに起こしていないこと及び改称により第9期の系列と接続しないことを明示した</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>No.39</t>
+          <t>No.40</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節</t>
+          <t>第2章第3節5</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>代表KPIは第9期計画の目標指標を引き継ぎ、別の指標を新たに起こしていないこと及び改称により第9期の系列と接続しないことを明示した</t>
+          <t>社会資源一覧の従業員数は延べの値となるため、供給の担い手の分析には施設単位の実人数を用いる旨を注に明示した</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
@@ -2698,17 +2698,17 @@
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>No.40</t>
+          <t>No.43</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節5</t>
+          <t>第2章第1節3・第5章 基本目標5</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数は延べの値となるため、供給の担い手の分析には施設単位の実人数を用いる旨を注に明示した</t>
+          <t>申請から二次判定までの平均所要日数が法定の30日を上回っていることを掲げ、期間の短縮を要介護認定の適正化の取組に加えた</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr"/>
@@ -2721,17 +2721,17 @@
       </c>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>No.43</t>
+          <t>No.45</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節3・第5章 基本目標5</t>
+          <t>第4章第3節・第5章 基本目標5・資料1</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>申請から二次判定までの平均所要日数が法定の30日を上回っていることを掲げ、期間の短縮を要介護認定の適正化の取組に加えた</t>
+          <t>代表KPI H15の分母を計画の標準給付費見込額とし、実績側は介護保険特別会計決算の保険給付費によることとした</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr"/>
@@ -2744,17 +2744,17 @@
       </c>
       <c r="B48" s="21" t="inlineStr">
         <is>
-          <t>No.45</t>
+          <t>No.57</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・第5章 基本目標5・資料1</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母を計画の標準給付費見込額とし、実績側は介護保険特別会計決算の保険給付費によることとした</t>
+          <t>第9期に計画値を0としていた認知症対応型通所介護は算定値を置き、介護療養型医療施設は計上しないこととした</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="B49" s="21" t="inlineStr">
         <is>
-          <t>No.57</t>
+          <t>No.58</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>第6章第2節・第4節1</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>第9期に計画値を0としていた認知症対応型通所介護は算定値を置き、介護療養型医療施設は計上しないこととした</t>
+          <t>定期巡回・随時対応型訪問介護看護及び看護小規模多機能型居宅介護は自然体の算定値を置き、整備又は事業の実施による上乗せは含めないこととした</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="B50" s="21" t="inlineStr">
         <is>
-          <t>No.58</t>
+          <t>No.63</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節・第4節1</t>
+          <t>第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護及び看護小規模多機能型居宅介護は自然体の算定値を置き、整備又は事業の実施による上乗せは含めないこととした</t>
+          <t>人口の基礎は案C（地方創生総合戦略と住民基本台帳の実績趨勢）のままとし、3町の人口目標を一律に用いられない理由を注に明示した</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B51" s="21" t="inlineStr">
         <is>
-          <t>No.63</t>
+          <t>No.65</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節・第6章第1節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>人口の基礎は案C（地方創生総合戦略と住民基本台帳の実績趨勢）のままとし、3町の人口目標を一律に用いられない理由を注に明示した</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとし、計画には優先順位そのものを掲げていない</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
@@ -2836,17 +2836,17 @@
       </c>
       <c r="B52" s="21" t="inlineStr">
         <is>
-          <t>No.65</t>
+          <t>No.66</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第2章第3節</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとし、計画には優先順位そのものを掲げていない</t>
+          <t>掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）によることとし、出所により事業所数が異なることは時点と把握の範囲の違いによる旨を注に明示した</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr"/>
@@ -2859,17 +2859,17 @@
       </c>
       <c r="B53" s="21" t="inlineStr">
         <is>
-          <t>No.66</t>
+          <t>No.67</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節</t>
+          <t>第6章第3節・第6節</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）によることとし、出所により事業所数が異なることは時点と把握の範囲の違いによる旨を注に明示した</t>
+          <t>当方の算定のまま進め、国の様式との対応は別に対照表として掲げることとし、その所在を第6章第6節の注に示した</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr"/>
@@ -2882,17 +2882,17 @@
       </c>
       <c r="B54" s="21" t="inlineStr">
         <is>
-          <t>No.67</t>
+          <t>No.68</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第6章第3節・第6節</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は別に対照表として掲げることとし、その所在を第6章第6節の注に示した</t>
+          <t>見える化システムの自然体推計の再出力を受けられないものとして、当方の要介護度別の算定を採り、見える化システムの値は社人研の推計人口を基礎とするものである旨を給付費の置き方の対比に明示した</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr"/>
@@ -2905,17 +2905,17 @@
       </c>
       <c r="B55" s="21" t="inlineStr">
         <is>
-          <t>No.68</t>
+          <t>No.70</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力を受けられないものとして、当方の要介護度別の算定を採り、見える化システムの値は社人研の推計人口を基礎とするものである旨を給付費の置き方の対比に明示した</t>
+          <t>保険者機能強化推進交付金等の全国順位は計画本文に掲げず、策定委員会の資料にとどめた（第3章第4節は対全国比までを掲げる）</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr"/>
@@ -2928,17 +2928,17 @@
       </c>
       <c r="B56" s="21" t="inlineStr">
         <is>
-          <t>No.70</t>
+          <t>No.73</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第5章 基本目標5</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の全国順位は計画本文に掲げず、策定委員会の資料にとどめた（第3章第4節は対全国比までを掲げる）</t>
+          <t>ケアプラン点検実施要領は協議資料にとどめ、計画本文には令和9年度当初に実施要領を定めることと点検件数・改善率・再指摘率の目標のみを掲げた</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
@@ -2951,17 +2951,17 @@
       </c>
       <c r="B57" s="21" t="inlineStr">
         <is>
-          <t>No.73</t>
+          <t>No.75</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領は協議資料にとどめ、計画本文には令和9年度当初に実施要領を定めることと点検件数・改善率・再指摘率の目標のみを掲げた</t>
+          <t>代表KPIと改善事項は当方の再整理案のままとし、計画本文の成果指標は現行の12項目のまま置いた（再整理案のご了承を受けた時点で置き換える）</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr"/>
@@ -2974,17 +2974,17 @@
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>No.75</t>
+          <t>No.76</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとし、計画本文の成果指標は現行の12項目のまま置いた（再整理案のご了承を受けた時点で置き換える）</t>
+          <t>代表KPI H03は、年齢階級別及び過年度分の抽出が確認できないため未算定のままとし、データ源と未算定である理由を注に明示した</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B59" s="21" t="inlineStr">
         <is>
-          <t>No.76</t>
+          <t>No.77</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H03は、年齢階級別及び過年度分の抽出が確認できないため未算定のままとし、データ源と未算定である理由を注に明示した</t>
+          <t>代表KPI H14は、北海道の評価指標⑥の団体別の値を引用できないものとして補完指標にとどめ、目標値を置かないこととした</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
@@ -3020,17 +3020,17 @@
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>No.77</t>
+          <t>No.78</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・資料1</t>
+          <t>第2章第3節</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H14は、北海道の評価指標⑥の団体別の値を引用できないものとして補完指標にとどめ、目標値を置かないこととした</t>
+          <t>認知症対応型共同生活介護の定員は北海道の名簿によるものとし、既存の事業所における定員の変更の有無は［要確認］として残した</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
@@ -3043,17 +3043,17 @@
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>No.78</t>
+          <t>No.79</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は北海道の名簿によるものとし、既存の事業所における定員の変更の有無は［要確認］として残した</t>
+          <t>第9期の19施策の体系を維持し、施策数の見直しは行わなかった</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr"/>
@@ -3066,17 +3066,17 @@
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>No.79</t>
+          <t>No.81</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章第3節・第5章 基本目標5・資料1</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持し、施策数の見直しは行わなかった</t>
+          <t>代表KPI H16は、給付実績の明細（加算・減算の単位）が得られないため、指定・指定の更新・運営指導の際に業務継続計画の策定を確認した地域密着型サービス事業所（17事業所）の割合に改めた</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="B63" s="21" t="inlineStr">
         <is>
-          <t>No.81</t>
+          <t>No.95</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・第5章 基本目標5・資料1</t>
+          <t>第6章第4節</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16は、給付実績の明細（加算・減算の単位）が得られないため、指定・指定の更新・運営指導の際に業務継続計画の策定を確認した地域密着型サービス事業所（17事業所）の割合に改めた</t>
+          <t>基準条例の内容は計画に掲げず、協力医療機関に関する規定を令和9年4月1日までに条例において整える必要があることを［要確認］として明示した</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr"/>
@@ -3112,17 +3112,17 @@
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>No.95</t>
+          <t>No.96</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第6章第4節</t>
+          <t>第2章第3節6・第6章第4節4</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>基準条例の内容は計画に掲げず、協力医療機関に関する規定を令和9年4月1日までに条例において整える必要があることを［要確認］として明示した</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げ、必要利用定員総数は3町への照会により定員を確定したうえで定めることを注に明示した</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
@@ -3135,17 +3135,17 @@
       </c>
       <c r="B65" s="21" t="inlineStr">
         <is>
-          <t>No.96</t>
+          <t>No.102</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節6・第6章第4節4</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げ、必要利用定員総数は3町への照会により定員を確定したうえで定めることを注に明示した</t>
+          <t>令和8年度（4か月）を基準年度に用いない旨を注に明示した</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr"/>
@@ -3158,17 +3158,17 @@
       </c>
       <c r="B66" s="21" t="inlineStr">
         <is>
-          <t>No.102</t>
+          <t>No.122</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を基準年度に用いない旨を注に明示した</t>
+          <t>転載を禁ずる旨の記載がある受領資料2件は成果品に用いず、原典のみを引いた（計画素案に当該2件からの記述はない）</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr"/>
@@ -3181,17 +3181,17 @@
       </c>
       <c r="B67" s="21" t="inlineStr">
         <is>
-          <t>No.122</t>
+          <t>No.30</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある受領資料2件は成果品に用いず、原典のみを引いた（計画素案に当該2件からの記述はない）</t>
+          <t>要介護度の構成は施設に入所している方と在宅の方を分けずに置き、入所の状況による重度化の見え方の違いを分けて算定していない旨を注に明示した</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr"/>
@@ -3204,17 +3204,17 @@
       </c>
       <c r="B68" s="21" t="inlineStr">
         <is>
-          <t>No.30</t>
+          <t>No.34</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>第6章第6節5</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>要介護度の構成は施設に入所している方と在宅の方を分けずに置き、入所の状況による重度化の見え方の違いを分けて算定していない旨を注に明示した</t>
+          <t>第9段階の割合1.630が国の標準1.700を下回ることと、設定の経緯を確認できていないため第9期の条例の割合をそのまま用いていることを注に明示した</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr"/>
@@ -3227,17 +3227,17 @@
       </c>
       <c r="B69" s="21" t="inlineStr">
         <is>
-          <t>No.34</t>
+          <t>No.35</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節5</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>第9段階の割合1.630が国の標準1.700を下回ることと、設定の経緯を確認できていないため第9期の条例の割合をそのまま用いていることを注に明示した</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は計画本文に掲げていない（保険料基準額の管内比較は北海道の公表資料により掲げている）</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr"/>
@@ -3250,17 +3250,17 @@
       </c>
       <c r="B70" s="21" t="inlineStr">
         <is>
-          <t>No.35</t>
+          <t>No.36</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節5</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は計画本文に掲げていない（保険料基準額の管内比較は北海道の公表資料により掲げている）</t>
+          <t>所得段階別の第1号被保険者数は令和6年度の実績の構成比を固定し、予定収納率は所得段階別の実績を確認できていないため全段階一律99.0％としている旨を明示した</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr"/>
@@ -3273,17 +3273,17 @@
       </c>
       <c r="B71" s="21" t="inlineStr">
         <is>
-          <t>No.36</t>
+          <t>No.115</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節5</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は令和6年度の実績の構成比を固定し、予定収納率は所得段階別の実績を確認できていないため全段階一律99.0％としている旨を明示した</t>
+          <t>令和9年4月1日に新設される3区分は実績がないため0として立て、国の様式の確定後に区分を改めることを注に明示した</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr"/>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="B72" s="21" t="inlineStr">
         <is>
-          <t>No.115</t>
+          <t>No.124</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日に新設される3区分は実績がないため0として立て、国の様式の確定後に区分を改めることを注に明示した</t>
+          <t>施設及び居住系サービスについても在宅と同じく令和7年度の要介護度別の利用率を固定し、これらに固有の伸びを別に選んでいない旨を注に明示した</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr"/>
@@ -3319,17 +3319,17 @@
       </c>
       <c r="B73" s="21" t="inlineStr">
         <is>
-          <t>No.124</t>
+          <t>No.140</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>第2章第5節・第4章第3節</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>施設及び居住系サービスについても在宅と同じく令和7年度の要介護度別の利用率を固定し、これらに固有の伸びを別に選んでいない旨を注に明示した</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合として用いることはできない旨を注に明示した</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr"/>
@@ -3342,17 +3342,17 @@
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>No.140</t>
+          <t>No.149</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第2章第5節・第4章第3節</t>
+          <t>第1章第2節・第8節</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合として用いることはできない旨を注に明示した</t>
+          <t>認知症基本法の条文を受領していないため、計画素案には条番号のみを書き項番号は書いていない</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr"/>
@@ -3365,17 +3365,17 @@
       </c>
       <c r="B75" s="21" t="inlineStr">
         <is>
-          <t>No.149</t>
+          <t>No.3</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第1章第2節・第8節</t>
+          <t>第2章第2節1</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領していないため、計画素案には条番号のみを書き項番号は書いていない</t>
+          <t>類似保険者との比較は全国・北海道・上川管内21保険者及び健康とくらしの調査の同規模保険者40団体によることとし、給付・供給面の選定条件は［要協議］のまま残した</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr"/>
@@ -3388,17 +3388,17 @@
       </c>
       <c r="B76" s="21" t="inlineStr">
         <is>
-          <t>No.1</t>
+          <t>No.4</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節1</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域の告示を確認できていないため、特定地域の基準①に該当するかどうかの判定は行わず［要確認］のまま残した</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標へ振り替え、振替後の定義・基準値・留意点を掲げた</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr"/>
@@ -3411,17 +3411,17 @@
       </c>
       <c r="B77" s="21" t="inlineStr">
         <is>
-          <t>No.3</t>
+          <t>No.5</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第2章第2節1</t>
+          <t>第3章第2節</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は全国・北海道・上川管内21保険者及び健康とくらしの調査の同規模保険者40団体によることとし、給付・供給面の選定条件は［要協議］のまま残した</t>
+          <t>第9期の施策・事業実績の提供を受けられない間は、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する旨を注に明示した</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr"/>
@@ -3434,17 +3434,17 @@
       </c>
       <c r="B78" s="21" t="inlineStr">
         <is>
-          <t>No.4</t>
+          <t>No.6</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・資料1</t>
+          <t>第3章第4節</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標へ振り替え、振替後の定義・基準値・留意点を掲げた</t>
+          <t>得点が0である項目について、取組がないのか要件を満たさないのか報告していないのかは公表資料から判別できない旨を注に明示した</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr"/>
@@ -3457,17 +3457,17 @@
       </c>
       <c r="B79" s="21" t="inlineStr">
         <is>
-          <t>No.5</t>
+          <t>No.8</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第3章第2節</t>
+          <t>第2章第5節</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績の提供を受けられない間は、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する旨を注に明示した</t>
+          <t>3調査の点検事項（母数・回答の偏り・重複・未回答施設）の取扱いは当方の判定のままとし、確定していないものは［要確認］として残した</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr"/>
@@ -3480,17 +3480,17 @@
       </c>
       <c r="B80" s="21" t="inlineStr">
         <is>
-          <t>No.6</t>
+          <t>No.19</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第3章第4節</t>
+          <t>第1章第5節</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>得点が0である項目について、取組がないのか要件を満たさないのか報告していないのかは公表資料から判別できない旨を注に明示した</t>
+          <t>意見公募手続は令和9年1月にウェブサイトにより2週間実施し概要版を併せて示すものとして掲げ、方法及び時期は［要協議］のまま残した</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr"/>
@@ -3503,17 +3503,17 @@
       </c>
       <c r="B81" s="21" t="inlineStr">
         <is>
-          <t>No.8</t>
+          <t>No.42</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第2章第5節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項（母数・回答の偏り・重複・未回答施設）の取扱いは当方の判定のままとし、確定していないものは［要確認］として残した</t>
+          <t>キックオフ会議資料の工程表は現行のまま進めた</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr"/>
@@ -3526,17 +3526,17 @@
       </c>
       <c r="B82" s="21" t="inlineStr">
         <is>
-          <t>No.19</t>
+          <t>No.9</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第1章第5節</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>意見公募手続は令和9年1月にウェブサイトにより2週間実施し概要版を併せて示すものとして掲げ、方法及び時期は［要協議］のまま残した</t>
+          <t>現に収録している対象者の範囲及び回収率によることとし、設問ごとに分母が異なることを注に明示した</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr"/>
@@ -3549,17 +3549,17 @@
       </c>
       <c r="B83" s="21" t="inlineStr">
         <is>
-          <t>No.42</t>
+          <t>No.10</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第2章第6節・第4章第3節</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料の工程表は現行のまま進めた</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）によることとし、代表KPI H14は各年9月30日現在の在籍者数を確認できないため未算定のままとした</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr"/>
@@ -3572,17 +3572,17 @@
       </c>
       <c r="B84" s="21" t="inlineStr">
         <is>
-          <t>No.9</t>
+          <t>No.11</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第2章第4節</t>
+          <t>第2章第1節</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者の範囲及び回収率によることとし、設問ごとに分母が異なることを注に明示した</t>
+          <t>町別・年齢4区分別の人口は令和5年までの各年10月1日現在の値であり、令和6年以降の趨勢は公表されている各年1月1日現在の値による（時点が9か月異なるため同じ系列としてつなげていない）旨を注に明示した</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr"/>
@@ -3595,17 +3595,17 @@
       </c>
       <c r="B85" s="21" t="inlineStr">
         <is>
-          <t>No.10</t>
+          <t>No.12</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第2章第6節・第4章第3節</t>
+          <t>第1章第7節</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）によることとし、代表KPI H14は各年9月30日現在の在籍者数を確認できないため未算定のままとした</t>
+          <t>基盤整備単位は3町（3圏域）とする案のままとし、圏域別の値は第9期計画による令和5年10月1日現在であること及び小学校区と6圏域の対応が確定していないことを注に明示した</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr"/>
@@ -3618,17 +3618,17 @@
       </c>
       <c r="B86" s="21" t="inlineStr">
         <is>
-          <t>No.11</t>
+          <t>No.18</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第2章第1節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>町別・年齢4区分別の人口は令和5年までの各年10月1日現在の値であり、令和6年以降の趨勢は公表されている各年1月1日現在の値による（時点が9か月異なるため同じ系列としてつなげていない）旨を注に明示した</t>
+          <t>骨子案は提出した内容のままとした</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr"/>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="B87" s="21" t="inlineStr">
         <is>
-          <t>No.12</t>
+          <t>No.22</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節</t>
+          <t>第1章第6節・第8節</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>基盤整備単位は3町（3圏域）とする案のままとし、圏域別の値は第9期計画による令和5年10月1日現在であること及び小学校区と6圏域の対応が確定していないことを注に明示した</t>
+          <t>北海道の評価指標のうち市町村数を単位とするものの読替えは当方の整理によることとし（読替えの方法は第8節の表）、考え方が示された場合は改める旨を第6節の注に明示した</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr"/>
@@ -3664,17 +3664,17 @@
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>No.18</t>
+          <t>No.27</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとした</t>
+          <t>前回との比較は第9期計画の本文に掲げられた指標に限り、検定は有効回答数を約4,700として行っている旨を注に明示した</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr"/>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>No.22</t>
+          <t>No.28</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第1章第6節・第8節</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標のうち市町村数を単位とするものの読替えは当方の整理によることとし（読替えの方法は第8節の表）、考え方が示された場合は改める旨を第6節の注に明示した</t>
+          <t>健康とくらしの調査の対象者に要支援者及び要介護者を含まないことと、他の調査と母集団が異なるため合算できないことを明示した</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr"/>
@@ -3710,17 +3710,17 @@
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>No.27</t>
+          <t>No.38</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第2章第4節</t>
+          <t>第3章第4節</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>前回との比較は第9期計画の本文に掲げられた指標に限り、検定は有効回答数を約4,700として行っている旨を注に明示した</t>
+          <t>公表されている全国集計の値によることとし、令和6年度分の評価は第8期の取組を反映したものであって評価の年度と取組の年度が一致しないことを注に明示した</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr"/>
@@ -3733,17 +3733,17 @@
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>No.28</t>
+          <t>No.46</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第2章第4節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の対象者に要支援者及び要介護者を含まないことと、他の調査と母集団が異なるため合算できないことを明示した</t>
+          <t>令和8年9月25日の再提供により決着した。再提供を受けたファイルの値（3町合計と要介護度別まで円単位一致）による</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr"/>
@@ -3756,17 +3756,17 @@
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>No.38</t>
+          <t>No.47</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第3章第4節</t>
+          <t>第6章第3節</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値によることとし、令和6年度分の評価は第8期の取組を反映したものであって評価の年度と取組の年度が一致しないことを注に明示した</t>
+          <t>給付費の実績は年報及び総括表詳細（保険者単位）によることとし、計画作成支援ツールの実績値は3町を合計しても保険者単位にならないため比較のためにのみ用いる旨を注に明示した</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr"/>
@@ -3779,17 +3779,17 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>No.46</t>
+          <t>No.48</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第3章第1節・第2節</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着した。再提供を受けたファイルの値（3町合計と要介護度別まで円単位一致）による</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値によることとし、参加率の分母が見える化システムのA系列であり住民基本台帳とは異なる旨を注に明示した</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr"/>
@@ -3802,17 +3802,17 @@
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>No.47</t>
+          <t>No.50</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第6章第3節</t>
+          <t>第3章第1節・第6章第6節</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>給付費の実績は年報及び総括表詳細（保険者単位）によることとし、計画作成支援ツールの実績値は3町を合計しても保険者単位にならないため比較のためにのみ用いる旨を注に明示した</t>
+          <t>受領済みの年報・月報の値によることとし、重度要介護認定率の実績は見える化システムの系列による6.3％であって年報から算定すると6.38％になること（判定は変わらない）を注に明示した</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr"/>
@@ -3825,17 +3825,17 @@
       </c>
       <c r="B95" s="21" t="inlineStr">
         <is>
-          <t>No.48</t>
+          <t>No.51</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第3章第1節・第2節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値によることとし、参加率の分母が見える化システムのA系列であり住民基本台帳とは異なる旨を注に明示した</t>
+          <t>月報の値の接続のずれは受領点検に記録として残し、計画本文には用いていない</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr"/>
@@ -3848,17 +3848,17 @@
       </c>
       <c r="B96" s="21" t="inlineStr">
         <is>
-          <t>No.50</t>
+          <t>No.52</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第3章第1節・第6章第6節</t>
+          <t>第3章第2節</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値によることとし、重度要介護認定率の実績は見える化システムの系列による6.3％であって年報から算定すると6.38％になること（判定は変わらない）を注に明示した</t>
+          <t>区分の名称及び科目は令和6年度決算書の表記によることとし、「一般介護予防事業費」の項がないことを注に明示した（地域支援事業費の総額は変わらない）</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr"/>
@@ -3871,17 +3871,17 @@
       </c>
       <c r="B97" s="21" t="inlineStr">
         <is>
-          <t>No.51</t>
+          <t>No.53</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは受領点検に記録として残し、計画本文には用いていない</t>
+          <t>財政調整基金を取り崩さないものとして算定し（不足する側に誤らない置き方）、1億円を取り崩した場合の月額への効きを併記した</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr"/>
@@ -3894,17 +3894,17 @@
       </c>
       <c r="B98" s="21" t="inlineStr">
         <is>
-          <t>No.52</t>
+          <t>No.54</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第3章第2節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>区分の名称及び科目は令和6年度決算書の表記によることとし、「一般介護予防事業費」の項がないことを注に明示した（地域支援事業費の総額は変わらない）</t>
+          <t>中間報告会議議事録の文書プロパティの作成者を法人名とし、個人名が入らない形で再出力した</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr"/>
@@ -3917,17 +3917,17 @@
       </c>
       <c r="B99" s="21" t="inlineStr">
         <is>
-          <t>No.53</t>
+          <t>No.55</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>財政調整基金を取り崩さないものとして算定し（不足する側に誤らない置き方）、1億円を取り崩した場合の月額への効きを併記した</t>
+          <t>議事録の表記に関するご提案3件（文のねじれ・並列の「及び」・文体）を本文へ反映した。受領版の表記のままとするご判断であれば戻す</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="B100" s="21" t="inlineStr">
         <is>
-          <t>No.54</t>
+          <t>No.56</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録の文書プロパティの作成者を法人名とし、個人名が入らない形で再出力した</t>
+          <t>他団体の要介護認定集計帳票6件は成果品に用いず、計画素案その他の成果品に当該団体名は現れない</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr"/>
@@ -3963,17 +3963,17 @@
       </c>
       <c r="B101" s="21" t="inlineStr">
         <is>
-          <t>No.55</t>
+          <t>No.59</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節4</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件（文のねじれ・並列の「及び」・文体）を本文へ反映した。受領版の表記のままとするご判断であれば戻す</t>
+          <t>調整交付金の算定基礎は標準給付費見込額と介護予防・日常生活支援総合事業費の合計であり包括的支援事業費及び任意事業費を含まないこと、この扱いにより第9期の公表値と一致することを注に明示した</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr"/>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B102" s="21" t="inlineStr">
         <is>
-          <t>No.56</t>
+          <t>No.61</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>他団体の要介護認定集計帳票6件は成果品に用いず、計画素案その他の成果品に当該団体名は現れない</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとし、計画本文には掲げていない（第9期施策別評価表による）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr"/>
@@ -4009,17 +4009,17 @@
       </c>
       <c r="B103" s="21" t="inlineStr">
         <is>
-          <t>No.59</t>
+          <t>No.80</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節4</t>
+          <t>第2章第6節</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎は標準給付費見込額と介護予防・日常生活支援総合事業費の合計であり包括的支援事業費及び任意事業費を含まないこと、この扱いにより第9期の公表値と一致することを注に明示した</t>
+          <t>重複の判別は職員個票の突合によらず当該事業所への照会により行う（個人情報を保管しない方針による）旨を明示した</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B104" s="21" t="inlineStr">
         <is>
-          <t>No.61</t>
+          <t>No.83</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとし、計画本文には掲げていない（第9期施策別評価表による）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで資料を整えた</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr"/>
@@ -4055,17 +4055,17 @@
       </c>
       <c r="B105" s="21" t="inlineStr">
         <is>
-          <t>No.80</t>
+          <t>No.85</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>第2章第6節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>重複の判別は職員個票の突合によらず当該事業所への照会により行う（個人情報を保管しない方針による）旨を明示した</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr"/>
@@ -4078,17 +4078,17 @@
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>No.83</t>
+          <t>No.60</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで資料を整えた</t>
+          <t>単価を令和7年度で固定し、施策反映・給付適正化・基金取崩しを織り込まない置き方であり、算定上の月額基準額は低い側の水準にあることを明示した</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr"/>
@@ -4101,17 +4101,17 @@
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>No.85</t>
+          <t>No.64</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>公表版 参考（介護サービスの内容）</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>区域内に事業所がないサービスも区域外の事業所を利用できること、通常の事業の実施地域の外では実費の負担が生じることがあることを住民向けの記載に加えた</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr"/>
@@ -4124,17 +4124,17 @@
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>No.60</t>
+          <t>No.69</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第3章第4節</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定し、施策反映・給付適正化・基金取崩しを織り込まない置き方であり、算定上の月額基準額は低い側の水準にあることを明示した</t>
+          <t>成果指向型配分枠は構成3町の回答の状況を確認できていないため第10期の施策に位置づけず、確認できた時点で判断する旨を注に明示した</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr"/>
@@ -4147,17 +4147,17 @@
       </c>
       <c r="B109" s="21" t="inlineStr">
         <is>
-          <t>No.64</t>
+          <t>No.89</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>公表版 参考（介護サービスの内容）</t>
+          <t>第1章第9節2</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスも区域外の事業所を利用できること、通常の事業の実施地域の外では実費の負担が生じることがあることを住民向けの記載に加えた</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr"/>
@@ -4170,17 +4170,17 @@
       </c>
       <c r="B110" s="21" t="inlineStr">
         <is>
-          <t>No.69</t>
+          <t>No.117</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第3章第4節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠は構成3町の回答の状況を確認できていないため第10期の施策に位置づけず、確認できた時点で判断する旨を注に明示した</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す現行の方針のままとした</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr"/>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>No.89</t>
+          <t>No.138</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ入力案とした</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>No.117</t>
+          <t>No.139</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す現行の方針のままとした</t>
+          <t>健康とくらしの調査の個票の再提供は依頼しない（成果品は収録済みで内容が確定しており不足がない）</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B113" s="21" t="inlineStr">
         <is>
-          <t>No.138</t>
+          <t>No.148</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ入力案とした</t>
+          <t>受領済みの画面の写しの範囲で入力値を示し、操作手引により確認できていない項目はその旨を明記した</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr"/>
@@ -4262,17 +4262,17 @@
       </c>
       <c r="B114" s="21" t="inlineStr">
         <is>
-          <t>No.139</t>
+          <t>No.90</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第2章第4節</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供は依頼しない（成果品は収録済みで内容が確定しており不足がない）</t>
+          <t>前回調査との比較は割合のみとし、指標別の分母を第9期計画の本文から確認できない旨を注に明示した</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr"/>
@@ -4285,17 +4285,17 @@
       </c>
       <c r="B115" s="21" t="inlineStr">
         <is>
-          <t>No.148</t>
+          <t>No.91</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第5章 基本目標5</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で入力値を示し、操作手引により確認できていない項目はその旨を明記した</t>
+          <t>給付実績の活用による確認等及び介護給付費通知は、実施の状況を確認したうえで第10期の実施の方針を定めることとし、現行の取組のまま位置づけた</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr"/>
@@ -4308,17 +4308,17 @@
       </c>
       <c r="B116" s="21" t="inlineStr">
         <is>
-          <t>No.90</t>
+          <t>No.92</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第2章第4節</t>
+          <t>第5章 基本目標5</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>前回調査との比較は割合のみとし、指標別の分母を第9期計画の本文から確認できない旨を注に明示した</t>
+          <t>認定調査の点検件数は、指定居宅介護支援事業所等への委託の状況を確認したうえで定める旨を注に明示した</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr"/>
@@ -4331,17 +4331,17 @@
       </c>
       <c r="B117" s="21" t="inlineStr">
         <is>
-          <t>No.91</t>
+          <t>No.97</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標5</t>
+          <t>第1章第9節1</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>給付実績の活用による確認等及び介護給付費通知は、実施の状況を確認したうえで第10期の実施の方針を定めることとし、現行の取組のまま位置づけた</t>
+          <t>条例の対応規定を確認していないため、省令の定めと対象事業所数（協力医療機関10事業所・生産性向上の取組に係る委員会15事業所）を示すにとどめた</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr"/>
@@ -4354,17 +4354,17 @@
       </c>
       <c r="B118" s="21" t="inlineStr">
         <is>
-          <t>No.92</t>
+          <t>No.99</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標5</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>認定調査の点検件数は、指定居宅介護支援事業所等への委託の状況を確認したうえで定める旨を注に明示した</t>
+          <t>過疎地域における小規模多機能型居宅介護の登録定員の超過の特例を用いずに見込量を算定している旨を注に明示した</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr"/>
@@ -4377,17 +4377,17 @@
       </c>
       <c r="B119" s="21" t="inlineStr">
         <is>
-          <t>No.97</t>
+          <t>No.108</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節1</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認していないため、省令の定めと対象事業所数（協力医療機関10事業所・生産性向上の取組に係る委員会15事業所）を示すにとどめた</t>
+          <t>補正を行っても開きが残る6種別は趨勢の置き方によるものではなく供給の状況又は制度の区分によるものであり、第4節の整備方針及び確保方策において扱う旨を注に明示した</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr"/>
@@ -4400,17 +4400,17 @@
       </c>
       <c r="B120" s="21" t="inlineStr">
         <is>
-          <t>No.99</t>
+          <t>No.111</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の登録定員の超過の特例を用いずに見込量を算定している旨を注に明示した</t>
+          <t>趨勢に現れない要因は給付費を増やす向きか減らす向きかを記すにとどめ、数値には織り込んでいない旨を注に明示した</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr"/>
@@ -4423,17 +4423,17 @@
       </c>
       <c r="B121" s="21" t="inlineStr">
         <is>
-          <t>No.108</t>
+          <t>No.118</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第5章 基本目標1</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>補正を行っても開きが残る6種別は趨勢の置き方によるものではなく供給の状況又は制度の区分によるものであり、第4節の整備方針及び確保方策において扱う旨を注に明示した</t>
+          <t>地域ケア会議の指標に施策化への転換率を加え、令和9年度に基準値を把握し令和10年度から目標値を置くこと、率とともに実数を併記すること、記録は3町が作成し集計値を提出することを明示した</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr"/>
@@ -4446,17 +4446,17 @@
       </c>
       <c r="B122" s="21" t="inlineStr">
         <is>
-          <t>No.111</t>
+          <t>No.119</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第5章 基本目標1</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は給付費を増やす向きか減らす向きかを記すにとどめ、数値には織り込んでいない旨を注に明示した</t>
+          <t>3町共通の記録様式は令和9年度に整えることとし、様式そのものは協議資料にとどめた</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B123" s="21" t="inlineStr">
         <is>
-          <t>No.118</t>
+          <t>No.120</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の指標に施策化への転換率を加え、令和9年度に基準値を把握し令和10年度から目標値を置くこと、率とともに実数を併記すること、記録は3町が作成し集計値を提出することを明示した</t>
+          <t>件数は地域ケア個別会議と地域ケア推進会議を分けずに計数する旨を注に明示した</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr"/>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="B124" s="21" t="inlineStr">
         <is>
-          <t>No.119</t>
+          <t>No.121</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>3町共通の記録様式は令和9年度に整えることとし、様式そのものは協議資料にとどめた</t>
+          <t>3町の実績は令和7年度の地域包括支援センター事業実施報告書により把握できる範囲で記述し、計数の単位が町により異なるため3町を合計できない旨を注に明示した</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr"/>
@@ -4515,17 +4515,17 @@
       </c>
       <c r="B125" s="21" t="inlineStr">
         <is>
-          <t>No.120</t>
+          <t>No.125</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標1</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>件数は地域ケア個別会議と地域ケア推進会議を分けずに計数する旨を注に明示した</t>
+          <t>認定率は年報（各年度末現在）によることとし、総括表（各年9月末現在）及び将来推計の参考シートの値との違いが時点等によるものである旨を注に明示した</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr"/>
@@ -4538,17 +4538,17 @@
       </c>
       <c r="B126" s="21" t="inlineStr">
         <is>
-          <t>No.121</t>
+          <t>No.127</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標1</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>3町の実績は令和7年度の地域包括支援センター事業実施報告書により把握できる範囲で記述し、計数の単位が町により異なるため3町を合計できない旨を注に明示した</t>
+          <t>人口の基礎は案C（地方創生総合戦略と住民基本台帳の実績趨勢）により、社人研の推計による場合との差を対比して掲げた</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr"/>
@@ -4561,17 +4561,17 @@
       </c>
       <c r="B127" s="21" t="inlineStr">
         <is>
-          <t>No.125</t>
+          <t>No.133</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>認定率は年報（各年度末現在）によることとし、総括表（各年9月末現在）及び将来推計の参考シートの値との違いが時点等によるものである旨を注に明示した</t>
+          <t>介護老人保健施設の令和8年度（4か月）の減少を将来へ延長していない旨を注に明示した</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr"/>
@@ -4584,17 +4584,17 @@
       </c>
       <c r="B128" s="21" t="inlineStr">
         <is>
-          <t>No.127</t>
+          <t>No.136</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>第6章第2節</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>人口の基礎は案C（地方創生総合戦略と住民基本台帳の実績趨勢）により、社人研の推計による場合との差を対比して掲げた</t>
+          <t>実績は年報（保険者単位）によることとし、見える化システムの画面が表示する令和7年度の値と一部の区分で食い違う旨を注に明示した</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr"/>
@@ -4607,17 +4607,17 @@
       </c>
       <c r="B129" s="21" t="inlineStr">
         <is>
-          <t>No.133</t>
+          <t>No.143</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>資料7</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度（4か月）の減少を将来へ延長していない旨を注に明示した</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとし、記号の意味と解消の方法を資料7に掲げた</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr"/>
@@ -4630,17 +4630,17 @@
       </c>
       <c r="B130" s="21" t="inlineStr">
         <is>
-          <t>No.136</t>
+          <t>No.154</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>実績は年報（保険者単位）によることとし、見える化システムの画面が表示する令和7年度の値と一部の区分で食い違う旨を注に明示した</t>
+          <t>町別の図は計画素案 第2章第1節に加えず、協議用の資料にとどめた</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr"/>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="B131" s="21" t="inlineStr">
         <is>
-          <t>No.143</t>
+          <t>No.157</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>資料7</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとし、記号の意味と解消の方法を資料7に掲げた</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとした</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr"/>
@@ -4676,17 +4676,17 @@
       </c>
       <c r="B132" s="21" t="inlineStr">
         <is>
-          <t>No.154</t>
+          <t>No.158</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第4章第3節・資料1</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>町別の図は計画素案 第2章第1節に加えず、協議用の資料にとどめた</t>
+          <t>代表KPI H06・H12の分母を設問ごとの有効回答とし、町別の値は掲げていない</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr"/>
@@ -4699,17 +4699,17 @@
       </c>
       <c r="B133" s="21" t="inlineStr">
         <is>
-          <t>No.157</t>
+          <t>No.159</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとした</t>
+          <t>通いの場の目標値は現在の実施の状況を前提として置き、整備が進む町がある場合は中間年の見直しで改める旨を注に明示した</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr"/>
@@ -4722,17 +4722,17 @@
       </c>
       <c r="B134" s="21" t="inlineStr">
         <is>
-          <t>No.158</t>
+          <t>No.160</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・資料1</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H06・H12の分母を設問ごとの有効回答とし、町別の値は掲げていない</t>
+          <t>認知症サポーターの養成は現に確認できる取組の範囲で掲げ、養成人数の目標値を置いていない旨を注に明示した</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="B135" s="21" t="inlineStr">
         <is>
-          <t>No.159</t>
+          <t>No.161</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>通いの場の目標値は現在の実施の状況を前提として置き、整備が進む町がある場合は中間年の見直しで改める旨を注に明示した</t>
+          <t>チームオレンジは東川町の取組として掲げ、他の町への展開は3町と協議して定める旨を注に明示した</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr"/>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B136" s="21" t="inlineStr">
         <is>
-          <t>No.160</t>
+          <t>No.162</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーターの養成は現に確認できる取組の範囲で掲げ、養成人数の目標値を置いていない旨を注に明示した</t>
+          <t>美瑛町の認知症初期集中支援推進事業は令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残した</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr"/>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="B137" s="21" t="inlineStr">
         <is>
-          <t>No.161</t>
+          <t>No.163</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標2</t>
+          <t>第3章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>チームオレンジは東川町の取組として掲げ、他の町への展開は3町と協議して定める旨を注に明示した</t>
+          <t>地域リハビリテーション活動支援事業は美瑛町の取組として記述し、3町展開とは書かないことに改めた</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr"/>
@@ -4814,17 +4814,17 @@
       </c>
       <c r="B138" s="21" t="inlineStr">
         <is>
-          <t>No.162</t>
+          <t>No.16</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標2</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業は令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残した</t>
+          <t>保険料算定の前提は単価固定・施策反映なし・適正化を織り込まない・基金取崩しなしによることを明示した（No.60と同じ前提）</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr"/>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="B139" s="21" t="inlineStr">
         <is>
-          <t>No.163</t>
+          <t>No.164</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>第3章第2節・第5章 基本目標2</t>
+          <t>第6章第4節4</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>地域リハビリテーション活動支援事業は美瑛町の取組として記述し、3町展開とは書かないことに改めた</t>
+          <t>美瑛町の地域密着型介護老人福祉施設は現定員の据え置き案を掲げ、本文は［要協議］のまま残した</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr"/>
@@ -4860,17 +4860,17 @@
       </c>
       <c r="B140" s="21" t="inlineStr">
         <is>
-          <t>No.16</t>
+          <t>No.165</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提は単価固定・施策反映なし・適正化を織り込まない・基金取崩しなしによることを明示した（No.60と同じ前提）</t>
+          <t>難聴高齢者の早期発見・早期介入は令和8年度に新たに加えられた交付金の評価項目であり町により得点に差があることを示し、現に確認できる範囲で掲げるにとどめた</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr"/>
@@ -4883,17 +4883,17 @@
       </c>
       <c r="B141" s="21" t="inlineStr">
         <is>
-          <t>No.164</t>
+          <t>No.166</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>第6章第4節4</t>
+          <t>第5章 基本目標2</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設は現定員の据え置き案を掲げ、本文は［要協議］のまま残した</t>
+          <t>通いの場の目標値は令和6年度の水準が続くものとして置いた</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr"/>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="B142" s="21" t="inlineStr">
         <is>
-          <t>No.165</t>
+          <t>No.167</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入は令和8年度に新たに加えられた交付金の評価項目であり町により得点に差があることを示し、現に確認できる範囲で掲げるにとどめた</t>
+          <t>認知症サポーター・ステップアップ講座は現に確認できる取組の範囲で記述し目標値を置いていない</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr"/>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="B143" s="21" t="inlineStr">
         <is>
-          <t>No.166</t>
+          <t>No.170</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>通いの場の目標値は令和6年度の水準が続くものとして置いた</t>
+          <t>計画素案から協議用の成果品へ移す8件を移し、「協議」判定の16件は素案に残した</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr"/>
@@ -4952,17 +4952,17 @@
       </c>
       <c r="B144" s="21" t="inlineStr">
         <is>
-          <t>No.167</t>
+          <t>No.172</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター・ステップアップ講座は現に確認できる取組の範囲で記述し目標値を置いていない</t>
+          <t>交付金の評価を示す図は計画本文に掲げず、策定委員会の資料にとどめた</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr"/>
@@ -4975,17 +4975,17 @@
       </c>
       <c r="B145" s="21" t="inlineStr">
         <is>
-          <t>No.170</t>
+          <t>No.174</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件を移し、「協議」判定の16件は素案に残した</t>
+          <t>人口及び第1号被保険者数は案Cにそろえ、見える化システムへの入力値も案Cによった</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr"/>
@@ -4998,17 +4998,17 @@
       </c>
       <c r="B146" s="21" t="inlineStr">
         <is>
-          <t>No.172</t>
+          <t>No.2</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第1章第9節1</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価を示す図は計画本文に掲げず、策定委員会の資料にとどめた</t>
+          <t>特定地域の指定に係る意向の表明は、基準及び手続が確定していないため行わないものとし、省令等の確定後に3町と協議して定める旨を注に明示した</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr"/>
@@ -5021,17 +5021,17 @@
       </c>
       <c r="B147" s="21" t="inlineStr">
         <is>
-          <t>No.174</t>
+          <t>No.13</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>第1章第7節</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数は案Cにそろえ、見える化システムへの入力値も案Cによった</t>
+          <t>訪問・通所困難地域は、北海道の指定事業所一覧の「通常の事業の実施地域」により判定することとした</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr"/>
@@ -5044,17 +5044,17 @@
       </c>
       <c r="B148" s="21" t="inlineStr">
         <is>
-          <t>No.2</t>
+          <t>No.14</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節1</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向の表明は、基準及び手続が確定していないため行わないものとし、省令等の確定後に3町と協議して定める旨を注に明示した</t>
+          <t>人口推計の基礎は案C（総合戦略と住民基本台帳の実績趨勢）による</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr"/>
@@ -5067,17 +5067,17 @@
       </c>
       <c r="B149" s="21" t="inlineStr">
         <is>
-          <t>No.13</t>
+          <t>No.15</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>第1章第7節</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域は、北海道の指定事業所一覧の「通常の事業の実施地域」により判定することとした</t>
+          <t>認定者数は年報の年度末現在を基準とし、月次推移は計画本文に掲げていない</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr"/>
@@ -5090,17 +5090,17 @@
       </c>
       <c r="B150" s="21" t="inlineStr">
         <is>
-          <t>No.14</t>
+          <t>No.17</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>資料2</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略と住民基本台帳の実績趨勢）による</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めず、役割分担と共通KPIにより接続することとした</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr"/>
@@ -5113,17 +5113,17 @@
       </c>
       <c r="B151" s="21" t="inlineStr">
         <is>
-          <t>No.15</t>
+          <t>No.20</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>第1章第8節</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末現在を基準とし、月次推移は計画本文に掲げていない</t>
+          <t>北海道の第9期支援計画の8基本目標との対応により整合を図った</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr"/>
@@ -5136,17 +5136,17 @@
       </c>
       <c r="B152" s="21" t="inlineStr">
         <is>
-          <t>No.17</t>
+          <t>No.21</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>資料2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めず、役割分担と共通KPIにより接続することとした</t>
+          <t>成果品の仕様は仕様書の定めによる</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr"/>
@@ -5159,17 +5159,17 @@
       </c>
       <c r="B153" s="21" t="inlineStr">
         <is>
-          <t>No.20</t>
+          <t>No.23</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>第1章第8節</t>
+          <t>第2章第3節6</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>北海道の第9期支援計画の8基本目標との対応により整合を図った</t>
+          <t>事業所の定員は北海道の各名簿及び介護サービス情報公表システムによることとし、未確認のものは［要確認］として残した</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr"/>
@@ -5182,17 +5182,17 @@
       </c>
       <c r="B154" s="21" t="inlineStr">
         <is>
-          <t>No.21</t>
+          <t>No.26</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第5章 基本目標2・基本目標3</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定めによる</t>
+          <t>認知症・医療介護連携の実績は、交付金の評価結果及び3町の地域包括支援センター事業実施報告書の範囲で記述した</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr"/>
@@ -5205,17 +5205,17 @@
       </c>
       <c r="B155" s="21" t="inlineStr">
         <is>
-          <t>No.23</t>
+          <t>No.29</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節6</t>
+          <t>第6章第1節</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員は北海道の各名簿及び介護サービス情報公表システムによることとし、未確認のものは［要確認］として残した</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定し、重度化は人口の高齢化による分のみを見込んだ</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr"/>
@@ -5228,17 +5228,17 @@
       </c>
       <c r="B156" s="21" t="inlineStr">
         <is>
-          <t>No.26</t>
+          <t>No.31</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・基本目標3</t>
+          <t>第6章第6節2</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績は、交付金の評価結果及び3町の地域包括支援センター事業実施報告書の範囲で記述した</t>
+          <t>給付適正化による抑制を推計に織り込まず、対象サービスの割合と10％抑制の効きを併記した</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr"/>
@@ -5251,17 +5251,17 @@
       </c>
       <c r="B157" s="21" t="inlineStr">
         <is>
-          <t>No.29</t>
+          <t>No.74</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>第6章第1節</t>
+          <t>第2章第3節6</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定し、重度化は人口の高齢化による分のみを見込んだ</t>
+          <t>家賃等の費用の水準は北海道における情報の収集を確認できないため把握しておらず、費用の面からの選択は扱っていない旨を注に明示した</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr"/>
@@ -5274,17 +5274,17 @@
       </c>
       <c r="B158" s="21" t="inlineStr">
         <is>
-          <t>No.31</t>
+          <t>No.144</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まず、対象サービスの割合と10％抑制の効きを併記した</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr"/>
@@ -5297,17 +5297,17 @@
       </c>
       <c r="B159" s="21" t="inlineStr">
         <is>
-          <t>No.74</t>
+          <t>No.156</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節6</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>家賃等の費用の水準は北海道における情報の収集を確認できないため把握しておらず、費用の面からの選択は扱っていない旨を注に明示した</t>
+          <t>所得段階別第1号被保険者数は当方の算定（16段階×8年度）により、所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr"/>
@@ -5320,17 +5320,17 @@
       </c>
       <c r="B160" s="21" t="inlineStr">
         <is>
-          <t>No.144</t>
+          <t>No.169</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第3章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけていない</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B161" s="21" t="inlineStr">
         <is>
-          <t>No.156</t>
+          <t>No.171</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数は当方の算定（16段階×8年度）により、所得段階の設定は弾力化を選ぶ</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr"/>
@@ -5366,17 +5366,17 @@
       </c>
       <c r="B162" s="21" t="inlineStr">
         <is>
-          <t>No.169</t>
+          <t>No.173</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>第3章第2節・第5章 基本目標2</t>
+          <t>―</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけていない</t>
+          <t>本文の図と別冊の図表集の対応は現行のままとした</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr"/>
@@ -5389,17 +5389,17 @@
       </c>
       <c r="B163" s="21" t="inlineStr">
         <is>
-          <t>No.171</t>
+          <t>No.24</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第6章第2節・第4節1</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せを行わなかった</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr"/>
@@ -5412,17 +5412,17 @@
       </c>
       <c r="B164" s="21" t="inlineStr">
         <is>
-          <t>No.173</t>
+          <t>No.25</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>第4章第3節・第5章</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>本文の図と別冊の図表集の対応は現行のままとした</t>
+          <t>代表KPIのうち基準値のないものは令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置くこととした</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr"/>
@@ -5435,17 +5435,17 @@
       </c>
       <c r="B165" s="21" t="inlineStr">
         <is>
-          <t>No.24</t>
+          <t>No.175</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節・第4節1</t>
+          <t>第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せを行わなかった</t>
+          <t>介護情報基盤の活用は本格運用開始日（令和10年4月1日）までに完了することを前提として記載し、年度ごとの事務の工程は［要確認］として残した。事業所への周知と登録の支援は広域連合・3町・事業者が担うものとして掲げた</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr"/>
@@ -5458,17 +5458,17 @@
       </c>
       <c r="B166" s="21" t="inlineStr">
         <is>
-          <t>No.25</t>
+          <t>No.176</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・第5章</t>
+          <t>第1章第9節5・第5章 基本目標4</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>代表KPIのうち基準値のないものは令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置くこととした</t>
+          <t>介護サービス事業者経営情報データベースは活用の方針のみを記載し、数値は掲げていない。用いられる範囲を確認して用いる旨を［要確認］として残した</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr"/>
@@ -5481,130 +5481,150 @@
       </c>
       <c r="B167" s="21" t="inlineStr">
         <is>
-          <t>No.175</t>
+          <t>No.177</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>第1章第9節5・第5章 基本目標3・基本目標4</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤の活用は本格運用開始日（令和10年4月1日）までに完了することを前提として記載し、年度ごとの事務の工程は［要確認］として残した。事業所への周知と登録の支援は広域連合・3町・事業者が担うものとして掲げた</t>
+          <t>都道府県との協定に基づく連携は北海道及び事業者とともに活用を検討する旨のみを記載し、市町村の役割が示された時点で関与の仕方を定めることとした</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr"/>
       <c r="F167" s="6" t="inlineStr"/>
       <c r="G167" s="6" t="inlineStr"/>
     </row>
-    <row r="168" ht="40" customHeight="1">
-      <c r="A168" s="5" t="n">
-        <v>163</v>
-      </c>
-      <c r="B168" s="21" t="inlineStr">
-        <is>
-          <t>No.176</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>第1章第9節5・第5章 基本目標4</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>介護サービス事業者経営情報データベースは活用の方針のみを記載し、数値は掲げていない。用いられる範囲を確認して用いる旨を［要確認］として残した</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr"/>
-      <c r="F168" s="6" t="inlineStr"/>
-      <c r="G168" s="6" t="inlineStr"/>
-    </row>
-    <row r="169" ht="40" customHeight="1">
-      <c r="A169" s="5" t="n">
-        <v>164</v>
-      </c>
-      <c r="B169" s="21" t="inlineStr">
-        <is>
-          <t>No.177</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>第1章第9節5・第5章 基本目標3・基本目標4</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>都道府県との協定に基づく連携は北海道及び事業者とともに活用を検討する旨のみを記載し、市町村の役割が示された時点で関与の仕方を定めることとした</t>
-        </is>
-      </c>
-      <c r="E169" s="6" t="inlineStr"/>
-      <c r="F169" s="6" t="inlineStr"/>
-      <c r="G169" s="6" t="inlineStr"/>
-    </row>
-    <row r="170"/>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="3" t="inlineStr">
+    <row r="168"/>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="32" customHeight="1">
-      <c r="A172" s="4" t="inlineStr"/>
-      <c r="B172" s="4" t="inlineStr">
+    <row r="170" ht="32" customHeight="1">
+      <c r="A170" s="4" t="inlineStr"/>
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>件名</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>決着しない場合の受託者の扱い</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
+      <c r="E170" s="4" t="inlineStr">
         <is>
           <t>宛先</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="G172" s="4" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B171" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F171" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B172" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>年報・月報の受領に伴う確認</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>受領済みの年報・月報の値による</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F172" s="21" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B173" s="21" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F173" s="21" t="inlineStr">
@@ -5620,19 +5640,19 @@
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B174" s="21" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -5653,19 +5673,19 @@
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B175" s="21" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -5686,19 +5706,19 @@
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B176" s="21" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -5719,19 +5739,19 @@
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B177" s="21" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -5752,19 +5772,19 @@
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B178" s="21" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -5785,24 +5805,24 @@
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B179" s="21" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F179" s="21" t="inlineStr">
@@ -5818,19 +5838,19 @@
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B180" s="21" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -5840,7 +5860,7 @@
       </c>
       <c r="F180" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
@@ -5851,24 +5871,24 @@
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B181" s="21" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F181" s="21" t="inlineStr">
@@ -5884,19 +5904,19 @@
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B182" s="21" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -5906,7 +5926,7 @@
       </c>
       <c r="F182" s="21" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
@@ -5917,19 +5937,19 @@
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B183" s="21" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -5950,19 +5970,19 @@
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B184" s="21" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -5983,24 +6003,24 @@
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B185" s="21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F185" s="21" t="inlineStr">
@@ -6016,19 +6036,19 @@
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B186" s="21" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -6049,19 +6069,19 @@
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B187" s="21" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
@@ -6076,25 +6096,25 @@
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部回答済</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B188" s="21" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -6115,19 +6135,19 @@
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B189" s="21" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -6142,25 +6162,25 @@
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B190" s="21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
@@ -6181,24 +6201,24 @@
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B191" s="21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F191" s="21" t="inlineStr">
@@ -6214,19 +6234,19 @@
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B192" s="21" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
@@ -6247,24 +6267,24 @@
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B193" s="21" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F193" s="21" t="inlineStr">
@@ -6280,24 +6300,24 @@
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B194" s="21" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F194" s="21" t="inlineStr">
@@ -6313,19 +6333,19 @@
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B195" s="21" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -6346,19 +6366,19 @@
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B196" s="21" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -6379,19 +6399,19 @@
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B197" s="21" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
@@ -6412,19 +6432,19 @@
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B198" s="21" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -6445,19 +6465,19 @@
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B199" s="21" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
@@ -6478,19 +6498,19 @@
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B200" s="21" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -6511,19 +6531,19 @@
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B201" s="21" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -6544,19 +6564,19 @@
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B202" s="21" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -6577,19 +6597,19 @@
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B203" s="21" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
@@ -6610,19 +6630,19 @@
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B204" s="21" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -6643,29 +6663,29 @@
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B205" s="21" t="n">
-        <v>147</v>
+        <v>2</v>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F205" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G205" s="6" t="inlineStr">
@@ -6676,29 +6696,29 @@
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B206" s="21" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F206" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
@@ -6709,19 +6729,19 @@
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" s="5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B207" s="21" t="n">
-        <v>151</v>
+        <v>15</v>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -6731,7 +6751,7 @@
       </c>
       <c r="F207" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G207" s="6" t="inlineStr">
@@ -6742,24 +6762,24 @@
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" s="5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B208" s="21" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F208" s="21" t="inlineStr">
@@ -6775,19 +6795,19 @@
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B209" s="21" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -6808,19 +6828,19 @@
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B210" s="21" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -6841,24 +6861,24 @@
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B211" s="21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F211" s="21" t="inlineStr">
@@ -6874,24 +6894,24 @@
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B212" s="21" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F212" s="21" t="inlineStr">
@@ -6907,19 +6927,19 @@
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" s="5" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B213" s="21" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
@@ -6940,24 +6960,24 @@
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" s="5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B214" s="21" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F214" s="21" t="inlineStr">
@@ -6973,19 +6993,19 @@
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B215" s="21" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
@@ -7006,19 +7026,19 @@
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" s="5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B216" s="21" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -7039,24 +7059,24 @@
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" s="5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B217" s="21" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F217" s="21" t="inlineStr">
@@ -7072,24 +7092,24 @@
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" s="5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B218" s="21" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F218" s="21" t="inlineStr">
@@ -7105,19 +7125,19 @@
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" s="5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B219" s="21" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -7138,19 +7158,19 @@
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B220" s="21" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -7171,24 +7191,24 @@
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B221" s="21" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F221" s="21" t="inlineStr">
@@ -7204,19 +7224,19 @@
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B222" s="21" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -7237,19 +7257,19 @@
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" s="5" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B223" s="21" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -7270,24 +7290,24 @@
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" s="5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B224" s="21" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F224" s="21" t="inlineStr">
@@ -7303,24 +7323,24 @@
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B225" s="21" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F225" s="21" t="inlineStr">
@@ -7336,19 +7356,19 @@
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B226" s="21" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -7369,19 +7389,19 @@
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" s="5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B227" s="21" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -7402,19 +7422,19 @@
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" s="5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B228" s="21" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -7435,19 +7455,19 @@
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" s="5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B229" s="21" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
@@ -7468,19 +7488,19 @@
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" s="5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B230" s="21" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -7501,19 +7521,19 @@
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B231" s="21" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -7534,24 +7554,24 @@
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B232" s="21" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F232" s="21" t="inlineStr">
@@ -7567,24 +7587,24 @@
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" s="5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B233" s="21" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F233" s="21" t="inlineStr">
@@ -7600,24 +7620,24 @@
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" s="5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B234" s="21" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F234" s="21" t="inlineStr">
@@ -7633,24 +7653,24 @@
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B235" s="21" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F235" s="21" t="inlineStr">
@@ -7666,24 +7686,24 @@
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" s="5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B236" s="21" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F236" s="21" t="inlineStr">
@@ -7699,19 +7719,19 @@
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B237" s="21" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
@@ -7732,24 +7752,24 @@
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" s="5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B238" s="21" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F238" s="21" t="inlineStr">
@@ -7765,19 +7785,19 @@
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B239" s="21" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
@@ -7798,19 +7818,19 @@
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" s="5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B240" s="21" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -7825,30 +7845,30 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部確認済み</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B241" s="21" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F241" s="21" t="inlineStr">
@@ -7864,19 +7884,19 @@
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" s="5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B242" s="21" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -7897,19 +7917,19 @@
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B243" s="21" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
@@ -7924,30 +7944,30 @@
       </c>
       <c r="G243" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>対応中</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B244" s="21" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F244" s="21" t="inlineStr">
@@ -7963,19 +7983,19 @@
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B245" s="21" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
@@ -7990,25 +8010,25 @@
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部解消</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" s="5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B246" s="21" t="n">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
@@ -8023,126 +8043,27 @@
       </c>
       <c r="G246" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="40" customHeight="1">
-      <c r="A247" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B247" s="21" t="n">
-        <v>164</v>
-      </c>
-      <c r="C247" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
-        </is>
-      </c>
-      <c r="D247" s="6" t="inlineStr">
-        <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E247" s="6" t="inlineStr">
-        <is>
-          <t>発注者・美瑛町</t>
-        </is>
-      </c>
-      <c r="F247" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G247" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="40" customHeight="1">
-      <c r="A248" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B248" s="21" t="n">
-        <v>170</v>
-      </c>
-      <c r="C248" s="6" t="inlineStr">
-        <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
-        </is>
-      </c>
-      <c r="D248" s="6" t="inlineStr">
-        <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
-        </is>
-      </c>
-      <c r="E248" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F248" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G248" s="6" t="inlineStr">
-        <is>
-          <t>一部解消</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="40" customHeight="1">
-      <c r="A249" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B249" s="21" t="n">
-        <v>174</v>
-      </c>
-      <c r="C249" s="6" t="inlineStr">
-        <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
-        </is>
-      </c>
-      <c r="D249" s="6" t="inlineStr">
-        <is>
-          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
-        </is>
-      </c>
-      <c r="E249" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F249" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G249" s="6" t="inlineStr">
-        <is>
           <t>未回答</t>
         </is>
       </c>
     </row>
-    <row r="250"/>
-    <row r="251" ht="48" customHeight="1">
-      <c r="A251" s="7" t="inlineStr">
-        <is>
-          <t>注1）仮置きにより計画素案へ反映した事項は164件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
-注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの77件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決172件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+    <row r="247"/>
+    <row r="248" ht="48" customHeight="1">
+      <c r="A248" s="7" t="inlineStr">
+        <is>
+          <t>注1）仮置きにより計画素案へ反映した事項は162件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
+注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。いずれにも決着しない場合の扱いを置いています。
+注3）未決173件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A169:G169"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A171:G171"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A251:G251"/>
+    <mergeCell ref="A248:G248"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8908,7 +8829,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>164件／台帳にないもの なし</t>
+          <t>162件／台帳にないもの なし</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -8933,7 +8854,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>77件／既定値のないもの なし</t>
+          <t>76件／既定値のないもの なし</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -956,7 +956,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>仮置きにより計画素案へ反映した162件と、令和8年10月30日までに決着をいただきたい事項。</t>
+          <t>仮置きにより計画素案へ反映した171件と、令和8年10月30日までに決着をいただきたい事項。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5498,369 +5498,279 @@
       <c r="F167" s="6" t="inlineStr"/>
       <c r="G167" s="6" t="inlineStr"/>
     </row>
-    <row r="168"/>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="32" customHeight="1">
-      <c r="A170" s="4" t="inlineStr"/>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>決着しない場合の受託者の扱い</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>宛先</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B168" s="21" t="inlineStr">
+        <is>
+          <t>No.178</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>第1章第2節・第1章第8節</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画が老人福祉法第20条の8の市町村老人福祉計画に当たり、介護保険事業計画と一体のものとして作成することとされていることを記載した。一体のものとする方法は［要協議］として残した</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr"/>
+      <c r="F168" s="6" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B169" s="21" t="inlineStr">
+        <is>
+          <t>No.179</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>第1章第2節・第5章 基本目標1</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する法律第14条による計画は構成3町が定めるものとして記載し、本計画は権利擁護の施策をもって接続することとした。中核機関の整備の状況は［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr"/>
+      <c r="F169" s="6" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr"/>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B170" s="21" t="inlineStr">
+        <is>
+          <t>No.180</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の避難確保計画を主な事業に置き、避難確保計画は業務継続計画とは別の計画であるため業務継続計画の策定率をもって作成の状況としないことを明記した。対象施設及び作成の状況は［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr"/>
+      <c r="F170" s="6" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr"/>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B171" s="21" t="n">
-        <v>40</v>
+        <v>166</v>
+      </c>
+      <c r="B171" s="21" t="inlineStr">
+        <is>
+          <t>No.182</t>
+        </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>第1章第9節6</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F171" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G171" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>社会保障審議会介護給付費分科会において検討されている事項があることまでを記載し、単位数、算定の要件及び施行の時期は書いていない</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr"/>
+      <c r="F171" s="6" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr"/>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B172" s="21" t="n">
-        <v>50</v>
+        <v>167</v>
+      </c>
+      <c r="B172" s="21" t="inlineStr">
+        <is>
+          <t>No.183</t>
+        </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>第6章第2節 注2</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F172" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>夜間対応型訪問介護は現行の区分のまま立て、令和9年4月1日に定期巡回・随時対応型訪問介護看護へ統合されることと、報酬上の経過措置の期限に2通りの記載があることを注に記載した</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr"/>
+      <c r="F172" s="6" t="inlineStr"/>
+      <c r="G172" s="6" t="inlineStr"/>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B173" s="21" t="n">
-        <v>52</v>
+        <v>168</v>
+      </c>
+      <c r="B173" s="21" t="inlineStr">
+        <is>
+          <t>No.184</t>
+        </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>第6章第2節 注1-1</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F173" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G173" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>短期入所生活介護は令和7年度（12か月の完結年度）の実績により算定し、積雪期の季節利用に係る例外及び長期利用減算の見直しが検討されていることを注に記載した</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr"/>
+      <c r="F173" s="6" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr"/>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B174" s="21" t="n">
-        <v>53</v>
+        <v>169</v>
+      </c>
+      <c r="B174" s="21" t="inlineStr">
+        <is>
+          <t>No.185</t>
+        </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>第1章第9節2</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
-        </is>
-      </c>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F174" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G174" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>小規模市町村地域支援連携協働体制整備事業を実施しないものとして地域支援事業費を算定し、該当する場合は費用の支弁の構造が変わることを記載した</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr"/>
+      <c r="F174" s="6" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr"/>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B175" s="21" t="n">
-        <v>63</v>
+        <v>170</v>
+      </c>
+      <c r="B175" s="21" t="inlineStr">
+        <is>
+          <t>No.186</t>
+        </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>第1章第9節2</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F175" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G175" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
+          <t>特定施設の定義のうち有料老人ホームが登録有料老人ホームに置き換わること（施行は公布の日から2年以内）を記載し、区域内3施設の扱いは［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr"/>
+      <c r="F175" s="6" t="inlineStr"/>
+      <c r="G175" s="6" t="inlineStr"/>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B176" s="21" t="n">
-        <v>65</v>
+        <v>171</v>
+      </c>
+      <c r="B176" s="21" t="inlineStr">
+        <is>
+          <t>No.188</t>
+        </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>第6章第3節2</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F176" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G176" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B177" s="21" t="n">
-        <v>67</v>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F177" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="40" customHeight="1">
-      <c r="A178" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B178" s="21" t="n">
-        <v>68</v>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F178" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="40" customHeight="1">
-      <c r="A179" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B179" s="21" t="n">
-        <v>78</v>
-      </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr">
-        <is>
-          <t>北海道の名簿の定員のまま概算する</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>発注者・美瑛町</t>
-        </is>
-      </c>
-      <c r="F179" s="21" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+          <t>地域支援事業費に政令で定める上限があることを記載し、令和6年度決算の水準を据え置いたまま算定していることを［要確認］として残した</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr"/>
+      <c r="F176" s="6" t="inlineStr"/>
+      <c r="G176" s="6" t="inlineStr"/>
+    </row>
+    <row r="177"/>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="4" t="inlineStr"/>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>決着しない場合の受託者の扱い</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>宛先</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B180" s="21" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F180" s="21" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
@@ -5871,24 +5781,24 @@
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B181" s="21" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F181" s="21" t="inlineStr">
@@ -5904,19 +5814,19 @@
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B182" s="21" t="n">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -5937,24 +5847,24 @@
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B183" s="21" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F183" s="21" t="inlineStr">
@@ -5970,19 +5880,19 @@
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B184" s="21" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -6003,19 +5913,19 @@
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B185" s="21" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
@@ -6036,19 +5946,19 @@
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B186" s="21" t="n">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
@@ -6069,19 +5979,19 @@
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B187" s="21" t="n">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
@@ -6096,30 +6006,30 @@
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B188" s="21" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F188" s="21" t="inlineStr">
@@ -6135,19 +6045,19 @@
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B189" s="21" t="n">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -6157,7 +6067,7 @@
       </c>
       <c r="F189" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G189" s="6" t="inlineStr">
@@ -6168,24 +6078,24 @@
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B190" s="21" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F190" s="21" t="inlineStr">
@@ -6201,24 +6111,24 @@
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B191" s="21" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F191" s="21" t="inlineStr">
@@ -6234,24 +6144,24 @@
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B192" s="21" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F192" s="21" t="inlineStr">
@@ -6267,19 +6177,19 @@
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" s="5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B193" s="21" t="n">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
@@ -6300,19 +6210,19 @@
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" s="5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B194" s="21" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
@@ -6333,19 +6243,19 @@
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" s="5" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B195" s="21" t="n">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
@@ -6366,19 +6276,19 @@
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" s="5" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B196" s="21" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
@@ -6393,25 +6303,25 @@
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部回答済</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" s="5" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B197" s="21" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
@@ -6432,19 +6342,19 @@
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" s="5" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B198" s="21" t="n">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -6465,19 +6375,19 @@
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B199" s="21" t="n">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
@@ -6498,24 +6408,24 @@
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" s="5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B200" s="21" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F200" s="21" t="inlineStr">
@@ -6531,19 +6441,19 @@
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" s="5" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B201" s="21" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -6564,19 +6474,19 @@
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" s="5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B202" s="21" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -6597,19 +6507,19 @@
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" s="5" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B203" s="21" t="n">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D203" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
@@ -6630,19 +6540,19 @@
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" s="5" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B204" s="21" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -6663,29 +6573,29 @@
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" s="5" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B205" s="21" t="n">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F205" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G205" s="6" t="inlineStr">
@@ -6696,29 +6606,29 @@
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" s="5" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B206" s="21" t="n">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F206" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G206" s="6" t="inlineStr">
@@ -6729,19 +6639,19 @@
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" s="5" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B207" s="21" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -6751,7 +6661,7 @@
       </c>
       <c r="F207" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G207" s="6" t="inlineStr">
@@ -6762,29 +6672,29 @@
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" s="5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B208" s="21" t="n">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F208" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G208" s="6" t="inlineStr">
@@ -6795,29 +6705,29 @@
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" s="5" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B209" s="21" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F209" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G209" s="6" t="inlineStr">
@@ -6828,19 +6738,19 @@
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" s="5" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B210" s="21" t="n">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -6850,7 +6760,7 @@
       </c>
       <c r="F210" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G210" s="6" t="inlineStr">
@@ -6861,19 +6771,19 @@
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" s="5" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B211" s="21" t="n">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
@@ -6883,7 +6793,7 @@
       </c>
       <c r="F211" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G211" s="6" t="inlineStr">
@@ -6894,19 +6804,19 @@
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" s="5" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B212" s="21" t="n">
-        <v>31</v>
+        <v>149</v>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -6916,7 +6826,7 @@
       </c>
       <c r="F212" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G212" s="6" t="inlineStr">
@@ -6927,19 +6837,19 @@
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" s="5" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B213" s="21" t="n">
-        <v>34</v>
+        <v>151</v>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
@@ -6949,7 +6859,7 @@
       </c>
       <c r="F213" s="21" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G213" s="6" t="inlineStr">
@@ -6960,24 +6870,24 @@
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" s="5" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B214" s="21" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F214" s="21" t="inlineStr">
@@ -6993,24 +6903,24 @@
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" s="5" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B215" s="21" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F215" s="21" t="inlineStr">
@@ -7026,19 +6936,19 @@
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" s="5" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B216" s="21" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -7059,24 +6969,24 @@
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" s="5" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B217" s="21" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F217" s="21" t="inlineStr">
@@ -7092,24 +7002,24 @@
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" s="5" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B218" s="21" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F218" s="21" t="inlineStr">
@@ -7125,19 +7035,19 @@
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" s="5" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B219" s="21" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -7158,19 +7068,19 @@
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" s="5" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B220" s="21" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -7191,24 +7101,24 @@
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" s="5" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B221" s="21" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F221" s="21" t="inlineStr">
@@ -7224,19 +7134,19 @@
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" s="5" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B222" s="21" t="n">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
@@ -7257,24 +7167,24 @@
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" s="5" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B223" s="21" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F223" s="21" t="inlineStr">
@@ -7290,19 +7200,19 @@
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" s="5" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B224" s="21" t="n">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -7323,24 +7233,24 @@
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" s="5" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B225" s="21" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F225" s="21" t="inlineStr">
@@ -7356,19 +7266,19 @@
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" s="5" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B226" s="21" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -7389,24 +7299,24 @@
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" s="5" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B227" s="21" t="n">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F227" s="21" t="inlineStr">
@@ -7422,24 +7332,24 @@
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" s="5" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B228" s="21" t="n">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F228" s="21" t="inlineStr">
@@ -7455,19 +7365,19 @@
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" s="5" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B229" s="21" t="n">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
@@ -7488,24 +7398,24 @@
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" s="5" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B230" s="21" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F230" s="21" t="inlineStr">
@@ -7521,24 +7431,24 @@
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" s="5" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B231" s="21" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F231" s="21" t="inlineStr">
@@ -7554,24 +7464,24 @@
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" s="5" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B232" s="21" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F232" s="21" t="inlineStr">
@@ -7587,24 +7497,24 @@
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" s="5" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B233" s="21" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F233" s="21" t="inlineStr">
@@ -7620,24 +7530,24 @@
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" s="5" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B234" s="21" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F234" s="21" t="inlineStr">
@@ -7653,19 +7563,19 @@
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" s="5" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B235" s="21" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -7686,19 +7596,19 @@
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" s="5" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="B236" s="21" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -7719,24 +7629,24 @@
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" s="5" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B237" s="21" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F237" s="21" t="inlineStr">
@@ -7752,24 +7662,24 @@
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" s="5" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B238" s="21" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F238" s="21" t="inlineStr">
@@ -7785,19 +7695,19 @@
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" s="5" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B239" s="21" t="n">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
@@ -7818,24 +7728,24 @@
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" s="5" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B240" s="21" t="n">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F240" s="21" t="inlineStr">
@@ -7845,30 +7755,30 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" s="5" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B241" s="21" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F241" s="21" t="inlineStr">
@@ -7884,24 +7794,24 @@
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" s="5" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B242" s="21" t="n">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F242" s="21" t="inlineStr">
@@ -7917,19 +7827,19 @@
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" s="5" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B243" s="21" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
@@ -7944,30 +7854,30 @@
       </c>
       <c r="G243" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" s="5" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B244" s="21" t="n">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F244" s="21" t="inlineStr">
@@ -7983,19 +7893,19 @@
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" s="5" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B245" s="21" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
@@ -8010,48 +7920,345 @@
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>一部解消</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B246" s="21" t="n">
+        <v>129</v>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの利用率等の伸びの選択</t>
+        </is>
+      </c>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F246" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B247" s="21" t="n">
+        <v>133</v>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+        </is>
+      </c>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+        </is>
+      </c>
+      <c r="E247" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F247" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G247" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B248" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
+        </is>
+      </c>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F248" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G248" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B249" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C249" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供</t>
+        </is>
+      </c>
+      <c r="D249" s="6" t="inlineStr">
+        <is>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+        </is>
+      </c>
+      <c r="E249" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F249" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G249" s="6" t="inlineStr">
+        <is>
+          <t>一部確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B250" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+        </is>
+      </c>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F250" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G250" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B251" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+        </is>
+      </c>
+      <c r="D251" s="6" t="inlineStr">
+        <is>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F251" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G251" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B252" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+        </is>
+      </c>
+      <c r="D252" s="6" t="inlineStr">
+        <is>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F252" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G252" s="6" t="inlineStr">
+        <is>
+          <t>対応中</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B253" s="21" t="n">
+        <v>164</v>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+        </is>
+      </c>
+      <c r="D253" s="6" t="inlineStr">
+        <is>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+        </is>
+      </c>
+      <c r="E253" s="6" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="F253" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G253" s="6" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B254" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+        </is>
+      </c>
+      <c r="D254" s="6" t="inlineStr">
+        <is>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+        </is>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F254" s="21" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G254" s="6" t="inlineStr">
+        <is>
+          <t>一部解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B246" s="21" t="n">
+      <c r="B255" s="21" t="n">
         <v>174</v>
       </c>
-      <c r="C246" s="6" t="inlineStr">
+      <c r="C255" s="6" t="inlineStr">
         <is>
           <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
-      <c r="D246" s="6" t="inlineStr">
+      <c r="D255" s="6" t="inlineStr">
         <is>
           <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E255" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F246" s="21" t="inlineStr">
+      <c r="F255" s="21" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G246" s="6" t="inlineStr">
+      <c r="G255" s="6" t="inlineStr">
         <is>
           <t>未回答</t>
         </is>
       </c>
     </row>
-    <row r="247"/>
-    <row r="248" ht="48" customHeight="1">
-      <c r="A248" s="7" t="inlineStr">
-        <is>
-          <t>注1）仮置きにより計画素案へ反映した事項は162件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
+    <row r="256"/>
+    <row r="257" ht="48" customHeight="1">
+      <c r="A257" s="7" t="inlineStr">
+        <is>
+          <t>注1）仮置きにより計画素案へ反映した事項は171件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
 注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。いずれにも決着しない場合の扱いを置いています。
 注3）未決173件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
@@ -8059,11 +8266,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A169:G169"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A248:G248"/>
+    <mergeCell ref="A257:G257"/>
+    <mergeCell ref="A178:G178"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8829,7 +9036,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>162件／台帳にないもの なし</t>
+          <t>171件／台帳にないもの なし</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_地域支援事業と必要利用定員総数" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_月額を動かす前提" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_見える化システムとの対照" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_残る未決と既定値" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_受託者案で確定した事項" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_10月30日までに行うこと" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_自己点検" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
@@ -1732,14 +1732,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>残る未決と既定値（決着しない場合の扱い）</t>
+          <t>受託者案で確定した事項（ご了承による）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。未決173件のすべてに「決着しない場合の受託者の扱い（既定値）」を置いており、ご決定をお待ちしている間も算定は止まりません。既定値は受託者の仮置きであり、決定ではありません。令和8年10月上旬の3町合同意見交換会で内容をお諮りします。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。令和8年10月19日のご了承により、ご決定をお待ちしていた173件はいずれも受託者案で確定しました。本概算はその内容によっています。うち13件は、保険料に関わる国の政令・省令・告示が示された後に再算定します。</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　仮置きにより計画素案へ反映した事項</t>
+          <t>1　受託者案により計画素案へ反映した事項</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2　第2次概算に効く未決の事項（期限が令和8年10月までのもの）</t>
+          <t>2　第2次概算に効く事項（期限が令和8年10月までのもの）</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>決着しない場合の受託者の扱い</t>
+          <t>ご了承いただいた受託者案</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="G184" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="G185" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G186" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="G187" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="G188" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="G189" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="G190" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="G191" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="G192" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="G193" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="G194" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G195" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="G196" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G197" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G198" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="G199" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="G200" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="G201" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="G202" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6534,7 @@
       </c>
       <c r="G203" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="G204" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="G205" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="G206" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="G207" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="G208" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="G209" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="G210" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G212" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="G214" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="G215" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="G218" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="G220" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="G222" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="G224" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="G226" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="G227" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G230" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="G231" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G232" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="G234" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G235" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="G236" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G238" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G239" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="G241" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="G242" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="G243" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="G244" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="G246" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="G248" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="G249" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="G250" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G251" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="G252" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="G253" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
       </c>
       <c r="G254" s="6" t="inlineStr">
         <is>
-          <t>一部解消</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="G255" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -8258,9 +8258,9 @@
     <row r="257" ht="48" customHeight="1">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>注1）仮置きにより計画素案へ反映した事項は171件です。作業として終えたことと、ご決定をお待ちしていることは別です。ご決定の内容が異なる場合は、その内容により置き直します。
-注2）2の表は、未決の事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。いずれにも決着しない場合の扱いを置いています。
-注3）未決173件の全体と優先順位は業務工程管理表 03_確認事項一覧によります。</t>
+          <t>注1）受託者案により計画素案へ反映した事項は171件です。ご了承の内容と異なるご判断をいただいた場合は、その内容により置き直します。
+注2）2の表は、受託者案で確定した事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。
+注3）受託者案で確定した173件の全体と、確認事項として挙げた経緯は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
+++ b/output/第10期計画_サービス見込量の算定_第2次概算.xlsx
@@ -1717,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:G256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1739,7 +1739,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。令和8年10月19日のご了承により、ご決定をお待ちしていた173件はいずれも受託者案で確定しました。本概算はその内容によっています。うち13件は、保険料に関わる国の政令・省令・告示が示された後に再算定します。</t>
+          <t>確認事項は業務工程管理表 03_確認事項一覧で一元管理しています。令和8年10月19日のご了承により、ご決定をお待ちしていた172件はいずれも受託者案で確定しました。本概算はその内容によっています。うち13件は、保険料に関わる国の政令・省令・告示が示された後に再算定します。</t>
         </is>
       </c>
     </row>
@@ -6807,16 +6807,16 @@
         <v>33</v>
       </c>
       <c r="B212" s="21" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -6840,31 +6840,31 @@
         <v>34</v>
       </c>
       <c r="B213" s="21" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F213" s="21" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -6873,21 +6873,21 @@
         <v>35</v>
       </c>
       <c r="B214" s="21" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F214" s="21" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="G214" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -6906,21 +6906,21 @@
         <v>36</v>
       </c>
       <c r="B215" s="21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F215" s="21" t="inlineStr">
@@ -6939,21 +6939,21 @@
         <v>37</v>
       </c>
       <c r="B216" s="21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F216" s="21" t="inlineStr">
@@ -6972,21 +6972,21 @@
         <v>38</v>
       </c>
       <c r="B217" s="21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F217" s="21" t="inlineStr">
@@ -7005,21 +7005,21 @@
         <v>39</v>
       </c>
       <c r="B218" s="21" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F218" s="21" t="inlineStr">
@@ -7038,16 +7038,16 @@
         <v>40</v>
       </c>
       <c r="B219" s="21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -7071,16 +7071,16 @@
         <v>41</v>
       </c>
       <c r="B220" s="21" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -7104,16 +7104,16 @@
         <v>42</v>
       </c>
       <c r="B221" s="21" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E221" s="6" t="inlineStr">
@@ -7137,21 +7137,21 @@
         <v>43</v>
       </c>
       <c r="B222" s="21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F222" s="21" t="inlineStr">
@@ -7170,21 +7170,21 @@
         <v>44</v>
       </c>
       <c r="B223" s="21" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F223" s="21" t="inlineStr">
@@ -7203,16 +7203,16 @@
         <v>45</v>
       </c>
       <c r="B224" s="21" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="G224" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7236,16 +7236,16 @@
         <v>46</v>
       </c>
       <c r="B225" s="21" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7269,21 +7269,21 @@
         <v>47</v>
       </c>
       <c r="B226" s="21" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F226" s="21" t="inlineStr">
@@ -7302,21 +7302,21 @@
         <v>48</v>
       </c>
       <c r="B227" s="21" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F227" s="21" t="inlineStr">
@@ -7335,16 +7335,16 @@
         <v>49</v>
       </c>
       <c r="B228" s="21" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7368,21 +7368,21 @@
         <v>50</v>
       </c>
       <c r="B229" s="21" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F229" s="21" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7401,21 +7401,21 @@
         <v>51</v>
       </c>
       <c r="B230" s="21" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F230" s="21" t="inlineStr">
@@ -7434,16 +7434,16 @@
         <v>52</v>
       </c>
       <c r="B231" s="21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -7467,16 +7467,16 @@
         <v>53</v>
       </c>
       <c r="B232" s="21" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G232" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7500,21 +7500,21 @@
         <v>54</v>
       </c>
       <c r="B233" s="21" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F233" s="21" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7533,21 +7533,21 @@
         <v>55</v>
       </c>
       <c r="B234" s="21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F234" s="21" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="G234" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7566,16 +7566,16 @@
         <v>56</v>
       </c>
       <c r="B235" s="21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="G235" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7599,21 +7599,21 @@
         <v>57</v>
       </c>
       <c r="B236" s="21" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F236" s="21" t="inlineStr">
@@ -7632,21 +7632,21 @@
         <v>58</v>
       </c>
       <c r="B237" s="21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F237" s="21" t="inlineStr">
@@ -7665,16 +7665,16 @@
         <v>59</v>
       </c>
       <c r="B238" s="21" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -7698,21 +7698,21 @@
         <v>60</v>
       </c>
       <c r="B239" s="21" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F239" s="21" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G239" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
     </row>
@@ -7731,16 +7731,16 @@
         <v>61</v>
       </c>
       <c r="B240" s="21" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -7764,16 +7764,16 @@
         <v>62</v>
       </c>
       <c r="B241" s="21" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
@@ -7797,21 +7797,21 @@
         <v>63</v>
       </c>
       <c r="B242" s="21" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F242" s="21" t="inlineStr">
@@ -7830,16 +7830,16 @@
         <v>64</v>
       </c>
       <c r="B243" s="21" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
@@ -7863,16 +7863,16 @@
         <v>65</v>
       </c>
       <c r="B244" s="21" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
       <c r="E244" s="6" t="inlineStr">
@@ -7896,16 +7896,16 @@
         <v>66</v>
       </c>
       <c r="B245" s="21" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
@@ -7929,21 +7929,21 @@
         <v>67</v>
       </c>
       <c r="B246" s="21" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F246" s="21" t="inlineStr">
@@ -7962,21 +7962,21 @@
         <v>68</v>
       </c>
       <c r="B247" s="21" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F247" s="21" t="inlineStr">
@@ -7995,16 +7995,16 @@
         <v>69</v>
       </c>
       <c r="B248" s="21" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -8028,16 +8028,16 @@
         <v>70</v>
       </c>
       <c r="B249" s="21" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
@@ -8061,16 +8061,16 @@
         <v>71</v>
       </c>
       <c r="B250" s="21" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -8094,16 +8094,16 @@
         <v>72</v>
       </c>
       <c r="B251" s="21" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
@@ -8127,21 +8127,21 @@
         <v>73</v>
       </c>
       <c r="B252" s="21" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F252" s="21" t="inlineStr">
@@ -8160,21 +8160,21 @@
         <v>74</v>
       </c>
       <c r="B253" s="21" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C253" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F253" s="21" t="inlineStr">
@@ -8193,16 +8193,16 @@
         <v>75</v>
       </c>
       <c r="B254" s="21" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -8221,46 +8221,13 @@
         </is>
       </c>
     </row>
-    <row r="255" ht="40" customHeight="1">
-      <c r="A255" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B255" s="21" t="n">
-        <v>174</v>
-      </c>
-      <c r="C255" s="6" t="inlineStr">
-        <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
-        </is>
-      </c>
-      <c r="D255" s="6" t="inlineStr">
-        <is>
-          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
-        </is>
-      </c>
-      <c r="E255" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F255" s="21" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G255" s="6" t="inlineStr">
-        <is>
-          <t>受託者案で確定</t>
-        </is>
-      </c>
-    </row>
-    <row r="256"/>
-    <row r="257" ht="48" customHeight="1">
-      <c r="A257" s="7" t="inlineStr">
+    <row r="255"/>
+    <row r="256" ht="48" customHeight="1">
+      <c r="A256" s="7" t="inlineStr">
         <is>
           <t>注1）受託者案により計画素案へ反映した事項は171件です。ご了承の内容と異なるご判断をいただいた場合は、その内容により置き直します。
-注2）2の表は、受託者案で確定した事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの76件です。
-注3）受託者案で確定した173件の全体と、確認事項として挙げた経緯は業務工程管理表 03_確認事項一覧によります。</t>
+注2）2の表は、受託者案で確定した事項のうち影響先にサービス見込量・給付費・保険料・計画素案 第6章を含み、期限が令和8年10月までのもの75件です。
+注3）受託者案で確定した172件の全体と、確認事項として挙げた経緯は業務工程管理表 03_確認事項一覧によります。</t>
         </is>
       </c>
     </row>
@@ -8268,8 +8235,8 @@
   <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A256:G256"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A257:G257"/>
     <mergeCell ref="A178:G178"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9061,7 +9028,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>76件／既定値のないもの なし</t>
+          <t>75件／既定値のないもの なし</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
